--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -267,13 +267,13 @@
     <t>Total SCHOOL CHOICE / CHOICE FUNDING</t>
   </si>
   <si>
-    <t>GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Total GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>Total PHILANTHROPY</t>
   </si>
   <si>
     <t>TOTAL NET REVENUE</t>
@@ -514,7 +514,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -558,7 +558,7 @@
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -582,7 +582,7 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1524,25 +1524,25 @@
       <c r="A12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="27" t="str">
         <f>SUM(B11:B11)</f>
-        <v>5000</v>
-      </c>
-      <c r="C12" s="27">
+        <v>0</v>
+      </c>
+      <c r="C12" s="27" t="str">
         <f>SUM(C11:C11)</f>
-        <v>6000</v>
-      </c>
-      <c r="D12" s="27">
+        <v>0</v>
+      </c>
+      <c r="D12" s="27" t="str">
         <f>SUM(D11:D11)</f>
-        <v>7000</v>
-      </c>
-      <c r="E12" s="27">
+        <v>0</v>
+      </c>
+      <c r="E12" s="27" t="str">
         <f>SUM(E11:E11)</f>
-        <v>8000</v>
-      </c>
-      <c r="F12" s="27">
+        <v>0</v>
+      </c>
+      <c r="F12" s="27" t="str">
         <f>SUM(F11:F11)</f>
-        <v>9000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -48,7 +48,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Microschool  •  LLC — Single Member  •  AZ</t>
+    <t>Microschool  •  LLC - Single Member  •  AZ</t>
   </si>
   <si>
     <t>Date Prepared</t>
@@ -102,7 +102,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Assumptions</t>
+    <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -126,7 +126,7 @@
     <t>Entity Type</t>
   </si>
   <si>
-    <t>LLC — Single Member</t>
+    <t>LLC - Single Member</t>
   </si>
   <si>
     <t>EIN</t>
@@ -279,7 +279,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Staffing &amp; Personnel</t>
+    <t>SchoolStack Budget - Staffing &amp; Personnel</t>
   </si>
   <si>
     <t>Role</t>
@@ -450,7 +450,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>KEY RATIOS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$B32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -258,6 +258,15 @@
     <t>Total TUITION &amp; STUDENT FEES</t>
   </si>
   <si>
+    <t>TUITION OFFSETS</t>
+  </si>
+  <si>
+    <t>Scholarship Discount</t>
+  </si>
+  <si>
+    <t>Total TUITION OFFSETS</t>
+  </si>
+  <si>
     <t>SCHOOL CHOICE / CHOICE FUNDING</t>
   </si>
   <si>
@@ -414,7 +423,7 @@
     <t>CAPITAL EXPENDITURES &amp; DEBT SERVICE</t>
   </si>
   <si>
-    <t>(No capital or debt items)</t>
+    <t>Equipment Loan</t>
   </si>
   <si>
     <t>TOTAL CAPITAL &amp; DEBT</t>
@@ -1293,7 +1302,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1445,24 +1454,24 @@
         <v>75</v>
       </c>
       <c r="B8" s="26">
-        <f>7000*Assumptions!B22</f>
-        <v>84000</v>
+        <f>-B4*0.1</f>
+        <v>-14400</v>
       </c>
       <c r="C8" s="26">
-        <f>7210*Assumptions!B23</f>
-        <v>129780</v>
+        <f>-C4*0.1</f>
+        <v>-22248</v>
       </c>
       <c r="D8" s="26">
-        <f>7426*Assumptions!B24</f>
-        <v>163372</v>
+        <f>-D4*0.1</f>
+        <v>-28008.2</v>
       </c>
       <c r="E8" s="26">
-        <f>7649*Assumptions!B25</f>
-        <v>191225</v>
+        <f>-E4*0.1</f>
+        <v>-32782.5</v>
       </c>
       <c r="F8" s="26">
-        <f>7878*Assumptions!B26</f>
-        <v>196950</v>
+        <f>-F4*0.1</f>
+        <v>-33765</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1471,23 +1480,23 @@
       </c>
       <c r="B9" s="27">
         <f>SUM(B8:B8)</f>
-        <v>84000</v>
+        <v>-14400</v>
       </c>
       <c r="C9" s="27">
         <f>SUM(C8:C8)</f>
-        <v>129780</v>
+        <v>-22248</v>
       </c>
       <c r="D9" s="27">
         <f>SUM(D8:D8)</f>
-        <v>163372</v>
+        <v>-28008</v>
       </c>
       <c r="E9" s="27">
         <f>SUM(E8:E8)</f>
-        <v>191225</v>
+        <v>-32782</v>
       </c>
       <c r="F9" s="27">
         <f>SUM(F8:F8)</f>
-        <v>196950</v>
+        <v>-33765</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1505,69 +1514,129 @@
         <v>78</v>
       </c>
       <c r="B11" s="26">
-        <v>5000</v>
+        <f>7000*Assumptions!B22</f>
+        <v>84000</v>
       </c>
       <c r="C11" s="26">
-        <v>6000</v>
+        <f>7210*Assumptions!B23</f>
+        <v>129780</v>
       </c>
       <c r="D11" s="26">
-        <v>7000</v>
+        <f>7426*Assumptions!B24</f>
+        <v>163372</v>
       </c>
       <c r="E11" s="26">
-        <v>8000</v>
+        <f>7649*Assumptions!B25</f>
+        <v>191225</v>
       </c>
       <c r="F11" s="26">
-        <v>9000</v>
+        <f>7878*Assumptions!B26</f>
+        <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="27" t="str">
+      <c r="B12" s="27">
         <f>SUM(B11:B11)</f>
+        <v>84000</v>
+      </c>
+      <c r="C12" s="27">
+        <f>SUM(C11:C11)</f>
+        <v>129780</v>
+      </c>
+      <c r="D12" s="27">
+        <f>SUM(D11:D11)</f>
+        <v>163372</v>
+      </c>
+      <c r="E12" s="27">
+        <f>SUM(E11:E11)</f>
+        <v>191225</v>
+      </c>
+      <c r="F12" s="27">
+        <f>SUM(F11:F11)</f>
+        <v>196950</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="26">
+        <v>5000</v>
+      </c>
+      <c r="C14" s="26">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="26">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="26">
+        <v>8000</v>
+      </c>
+      <c r="F14" s="26">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>SUM(B14:B14)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="27" t="str">
-        <f>SUM(C11:C11)</f>
+      <c r="C15" s="27" t="str">
+        <f>SUM(C14:C14)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="27" t="str">
-        <f>SUM(D11:D11)</f>
+      <c r="D15" s="27" t="str">
+        <f>SUM(D14:D14)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="27" t="str">
-        <f>SUM(E11:E11)</f>
+      <c r="E15" s="27" t="str">
+        <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="27" t="str">
-        <f>SUM(F11:F11)</f>
+      <c r="F15" s="27" t="str">
+        <f>SUM(F14:F14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="27">
-        <f>B6+B9+B12</f>
-        <v>236000</v>
-      </c>
-      <c r="C14" s="27">
-        <f>C6+C9+C12</f>
-        <v>362760</v>
-      </c>
-      <c r="D14" s="27">
-        <f>D6+D9+D12</f>
-        <v>455954</v>
-      </c>
-      <c r="E14" s="27">
-        <f>E6+E9+E12</f>
-        <v>533300</v>
-      </c>
-      <c r="F14" s="27">
-        <f>F6+F9+F12</f>
-        <v>549850</v>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="27">
+        <f>B6+B9+B12+B15</f>
+        <v>221600</v>
+      </c>
+      <c r="C17" s="27">
+        <f>C6+C9+C12+C15</f>
+        <v>340512</v>
+      </c>
+      <c r="D17" s="27">
+        <f>D6+D9+D12+D15</f>
+        <v>427946</v>
+      </c>
+      <c r="E17" s="27">
+        <f>E6+E9+E12+E15</f>
+        <v>500518</v>
+      </c>
+      <c r="F17" s="27">
+        <f>F6+F9+F12+F15</f>
+        <v>516085</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1663,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1606,39 +1675,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D4" s="28">
         <v>1</v>
@@ -1658,13 +1727,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" s="28">
         <v>1</v>
@@ -1684,13 +1753,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D6" s="28">
         <v>0.5</v>
@@ -1710,7 +1779,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1722,7 +1791,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B9" s="20">
         <v>3</v>
@@ -1730,7 +1799,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B10" s="20">
         <v>2.5</v>
@@ -1738,7 +1807,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" s="29">
         <v>114000</v>
@@ -1746,7 +1815,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B12" s="29">
         <v>20000</v>
@@ -1754,7 +1823,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="29">
         <v>8721</v>
@@ -1762,7 +1831,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B14" s="29">
         <v>0</v>
@@ -1770,7 +1839,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="31">
         <v>142721</v>
@@ -1778,7 +1847,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1808,7 +1877,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B19" s="26">
         <v>142721</v>
@@ -1828,7 +1897,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B20" s="32">
         <f>(1+Assumptions!B29)^0</f>
@@ -1853,7 +1922,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B21" s="33">
         <f>Assumptions!B31</f>
@@ -1874,7 +1943,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B22" s="27">
         <f>B19*B20*B21</f>
@@ -1969,7 +2038,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B4" s="26">
         <f>500*Assumptions!B22</f>
@@ -2004,7 +2073,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B5" s="27">
         <f>SUM(B4:B4)</f>
@@ -2029,7 +2098,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2039,7 +2108,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="26">
         <f>300*Assumptions!B22</f>
@@ -2064,7 +2133,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B8" s="27">
         <f>SUM(B7:B7)</f>
@@ -2089,7 +2158,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2099,7 +2168,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B10" s="26">
         <f>2500*12</f>
@@ -2124,7 +2193,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B11" s="26">
         <f>300*12</f>
@@ -2149,7 +2218,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B12" s="26">
         <v>2400</v>
@@ -2169,7 +2238,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B13" s="27">
         <f>SUM(B10:B12)</f>
@@ -2194,7 +2263,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2204,7 +2273,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B15" s="26">
         <v>3000</v>
@@ -2224,7 +2293,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B16" s="27">
         <f>SUM(B15:B15)</f>
@@ -2249,7 +2318,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B18" s="27">
         <f>B5+B8+B13+B16</f>
@@ -2316,7 +2385,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2326,42 +2395,47 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B3" s="26">
-        <v>0</v>
+        <v>6959.808550594178</v>
       </c>
       <c r="C3" s="26">
-        <v>0</v>
+        <v>6959.808550594178</v>
       </c>
       <c r="D3" s="26">
-        <v>0</v>
+        <v>6959.808550594178</v>
       </c>
       <c r="E3" s="26">
-        <v>0</v>
+        <v>6959.808550594178</v>
       </c>
       <c r="F3" s="26">
-        <v>0</v>
+        <v>6959.808550594178</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B4" s="27">
-        <v>0</v>
+        <f>SUM(B3:B3)</f>
+        <v>6960</v>
       </c>
       <c r="C4" s="27">
-        <v>0</v>
+        <f>SUM(C3:C3)</f>
+        <v>6960</v>
       </c>
       <c r="D4" s="27">
-        <v>0</v>
+        <f>SUM(D3:D3)</f>
+        <v>6960</v>
       </c>
       <c r="E4" s="27">
-        <v>0</v>
+        <f>SUM(E3:E3)</f>
+        <v>6960</v>
       </c>
       <c r="F4" s="27">
-        <v>0</v>
+        <f>SUM(F3:F3)</f>
+        <v>6960</v>
       </c>
     </row>
   </sheetData>
@@ -2408,32 +2482,32 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B2" s="26">
-        <f>'Revenue Schedule'!B14</f>
-        <v>236000</v>
+        <f>'Revenue Schedule'!B17</f>
+        <v>221600</v>
       </c>
       <c r="C2" s="26">
-        <f>'Revenue Schedule'!C14</f>
-        <v>362760</v>
+        <f>'Revenue Schedule'!C17</f>
+        <v>340512</v>
       </c>
       <c r="D2" s="26">
-        <f>'Revenue Schedule'!D14</f>
-        <v>455954</v>
+        <f>'Revenue Schedule'!D17</f>
+        <v>427946</v>
       </c>
       <c r="E2" s="26">
-        <f>'Revenue Schedule'!E14</f>
-        <v>533300</v>
+        <f>'Revenue Schedule'!E17</f>
+        <v>500518</v>
       </c>
       <c r="F2" s="26">
-        <f>'Revenue Schedule'!F14</f>
-        <v>549850</v>
+        <f>'Revenue Schedule'!F17</f>
+        <v>516085</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B3" s="26">
         <f>'Staffing &amp; Personnel'!B22</f>
@@ -2485,100 +2559,100 @@
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26" t="str">
+      <c r="B5" s="26">
         <f>'Capital &amp; Debt'!B4</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="26" t="str">
+        <v>6960</v>
+      </c>
+      <c r="C5" s="26">
         <f>'Capital &amp; Debt'!C4</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="26" t="str">
+        <v>6960</v>
+      </c>
+      <c r="D5" s="26">
         <f>'Capital &amp; Debt'!D4</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="26" t="str">
+        <v>6960</v>
+      </c>
+      <c r="E5" s="26">
         <f>'Capital &amp; Debt'!E4</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="26" t="str">
+        <v>6960</v>
+      </c>
+      <c r="F5" s="26">
         <f>'Capital &amp; Debt'!F4</f>
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B6" s="27">
         <f>B3+B4+B5</f>
-        <v>167534</v>
+        <v>174494</v>
       </c>
       <c r="C6" s="27">
         <f>C3+C4+C5</f>
-        <v>201966</v>
+        <v>208926</v>
       </c>
       <c r="D6" s="27">
         <f>D3+D4+D5</f>
-        <v>211359</v>
+        <v>218319</v>
       </c>
       <c r="E6" s="27">
         <f>E3+E4+E5</f>
-        <v>220293</v>
+        <v>227253</v>
       </c>
       <c r="F6" s="27">
         <f>F3+F4+F5</f>
-        <v>226848</v>
+        <v>233808</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B7" s="27">
         <f>B2-B6</f>
-        <v>68466</v>
+        <v>47106</v>
       </c>
       <c r="C7" s="27">
         <f>C2-C6</f>
-        <v>160794</v>
+        <v>131586</v>
       </c>
       <c r="D7" s="27">
         <f>D2-D6</f>
-        <v>244595</v>
+        <v>209627</v>
       </c>
       <c r="E7" s="27">
         <f>E2-E6</f>
-        <v>313007</v>
+        <v>273265</v>
       </c>
       <c r="F7" s="27">
         <f>F2-F6</f>
-        <v>323002</v>
+        <v>282277</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B8" s="26">
         <f>B7</f>
-        <v>68466</v>
+        <v>47106</v>
       </c>
       <c r="C8" s="26">
         <f>B8+C7</f>
-        <v>229260</v>
+        <v>178692</v>
       </c>
       <c r="D8" s="26">
         <f>C8+D7</f>
-        <v>473855</v>
+        <v>388319</v>
       </c>
       <c r="E8" s="26">
         <f>D8+E7</f>
-        <v>786862</v>
+        <v>661584</v>
       </c>
       <c r="F8" s="26">
         <f>E8+F7</f>
-        <v>1109864</v>
+        <v>943861</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2587,23 +2661,23 @@
       </c>
       <c r="B9" s="34">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
-        <v>4.904031420487782</v>
+        <v>3.2394924753859735</v>
       </c>
       <c r="C9" s="34">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
-        <v>13.621698701761682</v>
+        <v>10.263461704144051</v>
       </c>
       <c r="D9" s="34">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
-        <v>26.90332562133621</v>
+        <v>21.34412488148077</v>
       </c>
       <c r="E9" s="34">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
-        <v>42.86266018439079</v>
+        <v>34.93466752914153</v>
       </c>
       <c r="F9" s="34">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
-        <v>58.71053745239103</v>
+        <v>48.44287620611784</v>
       </c>
     </row>
   </sheetData>
@@ -2630,7 +2704,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -2640,7 +2714,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2714,12 +2788,12 @@
         <v>37</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2774,10 +2848,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C17" s="37">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
@@ -2818,32 +2892,32 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B20" s="26">
         <f>'Financial Model'!B2</f>
-        <v>236000</v>
+        <v>221600</v>
       </c>
       <c r="C20" s="26">
         <f>'Financial Model'!C2</f>
-        <v>362760</v>
+        <v>340512</v>
       </c>
       <c r="D20" s="26">
         <f>'Financial Model'!D2</f>
-        <v>455954</v>
+        <v>427946</v>
       </c>
       <c r="E20" s="26">
         <f>'Financial Model'!E2</f>
-        <v>533300</v>
+        <v>500518</v>
       </c>
       <c r="F20" s="26">
         <f>'Financial Model'!F2</f>
-        <v>549850</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B21" s="26">
         <f>'Financial Model'!B3</f>
@@ -2893,77 +2967,77 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B23" s="27">
         <f>'Financial Model'!B6</f>
-        <v>167534</v>
+        <v>174494</v>
       </c>
       <c r="C23" s="27">
         <f>'Financial Model'!C6</f>
-        <v>201966</v>
+        <v>208926</v>
       </c>
       <c r="D23" s="27">
         <f>'Financial Model'!D6</f>
-        <v>211359</v>
+        <v>218319</v>
       </c>
       <c r="E23" s="27">
         <f>'Financial Model'!E6</f>
-        <v>220293</v>
+        <v>227253</v>
       </c>
       <c r="F23" s="27">
         <f>'Financial Model'!F6</f>
-        <v>226848</v>
+        <v>233808</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B24" s="38">
         <f>'Financial Model'!B7</f>
-        <v>68466</v>
+        <v>47106</v>
       </c>
       <c r="C24" s="38">
         <f>'Financial Model'!C7</f>
-        <v>160794</v>
+        <v>131586</v>
       </c>
       <c r="D24" s="38">
         <f>'Financial Model'!D7</f>
-        <v>244595</v>
+        <v>209627</v>
       </c>
       <c r="E24" s="38">
         <f>'Financial Model'!E7</f>
-        <v>313007</v>
+        <v>273265</v>
       </c>
       <c r="F24" s="38">
         <f>'Financial Model'!F7</f>
-        <v>323002</v>
+        <v>282277</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B25" s="26">
         <f>'Financial Model'!B8</f>
-        <v>68466</v>
+        <v>47106</v>
       </c>
       <c r="C25" s="26">
         <f>'Financial Model'!C8</f>
-        <v>229260</v>
+        <v>178692</v>
       </c>
       <c r="D25" s="26">
         <f>'Financial Model'!D8</f>
-        <v>473855</v>
+        <v>388319</v>
       </c>
       <c r="E25" s="26">
         <f>'Financial Model'!E8</f>
-        <v>786862</v>
+        <v>661584</v>
       </c>
       <c r="F25" s="26">
         <f>'Financial Model'!F8</f>
-        <v>1109864</v>
+        <v>943861</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2972,28 +3046,28 @@
       </c>
       <c r="B26" s="13">
         <f>'Financial Model'!B9</f>
-        <v>4.904031420487782</v>
+        <v>3.2394924753859735</v>
       </c>
       <c r="C26" s="13">
         <f>'Financial Model'!C9</f>
-        <v>13.621698701761682</v>
+        <v>10.263461704144051</v>
       </c>
       <c r="D26" s="13">
         <f>'Financial Model'!D9</f>
-        <v>26.90332562133621</v>
+        <v>21.34412488148077</v>
       </c>
       <c r="E26" s="13">
         <f>'Financial Model'!E9</f>
-        <v>42.86266018439079</v>
+        <v>34.93466752914153</v>
       </c>
       <c r="F26" s="13">
         <f>'Financial Model'!F9</f>
-        <v>58.71053745239103</v>
+        <v>48.44287620611784</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3003,107 +3077,107 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B29" s="26">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>19666.666666666668</v>
+        <v>18466.666666666668</v>
       </c>
       <c r="C29" s="26">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>20153.333333333332</v>
+        <v>18917.333333333332</v>
       </c>
       <c r="D29" s="26">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>20725.18181818182</v>
+        <v>19452.090909090908</v>
       </c>
       <c r="E29" s="26">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>21332</v>
+        <v>20020.72</v>
       </c>
       <c r="F29" s="26">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>21994</v>
+        <v>20643.4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B30" s="37">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.5039576271186441</v>
+        <v>0.5367057761732852</v>
       </c>
       <c r="C30" s="37">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.4052348660271254</v>
+        <v>0.43171165773893433</v>
       </c>
       <c r="D30" s="37">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.33207955188461996</v>
+        <v>0.3538133315885649</v>
       </c>
       <c r="E30" s="37">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.2924339021188824</v>
+        <v>0.31158719566529075</v>
       </c>
       <c r="F30" s="37">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.2921414931344912</v>
+        <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B31" s="37">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
-        <v>0.2059322033898305</v>
+        <v>0.21931407942238268</v>
       </c>
       <c r="C31" s="37">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
-        <v>0.1515133972874628</v>
+        <v>0.16141281364533408</v>
       </c>
       <c r="D31" s="37">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
-        <v>0.13147378902257684</v>
+        <v>0.14007842110920538</v>
       </c>
       <c r="E31" s="37">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
-        <v>0.12064129008063004</v>
+        <v>0.12854282962850486</v>
       </c>
       <c r="F31" s="37">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
-        <v>0.12042193325452397</v>
+        <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
-        <v>0.2901101694915254</v>
+        <v>0.21257220216606498</v>
       </c>
       <c r="C32" s="12">
         <f>IF(C20=0,0,C24/C20)</f>
-        <v>0.44325173668541185</v>
+        <v>0.38643572032703694</v>
       </c>
       <c r="D32" s="12">
         <f>IF(D20=0,0,D24/D20)</f>
-        <v>0.5364466590928032</v>
+        <v>0.4898445130927734</v>
       </c>
       <c r="E32" s="12">
         <f>IF(E20=0,0,E24/E20)</f>
-        <v>0.5869248078004875</v>
+        <v>0.5459643809013862</v>
       </c>
       <c r="F32" s="12">
         <f>IF(F20=0,0,F24/F20)</f>
-        <v>0.5874365736109848</v>
+        <v>0.5469583498842245</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3113,62 +3187,62 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B35" s="37">
-        <v>0.6228813559322034</v>
+        <v>0.5983754512635379</v>
       </c>
       <c r="C35" s="37">
-        <v>0.6257029440952696</v>
+        <v>0.6012475331265859</v>
       </c>
       <c r="D35" s="37">
-        <v>0.626339499160003</v>
+        <v>0.6018841638357006</v>
       </c>
       <c r="E35" s="37">
-        <v>0.6264297768610538</v>
+        <v>0.6019619693617106</v>
       </c>
       <c r="F35" s="37">
-        <v>0.6254433027189233</v>
+        <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B36" s="37">
-        <v>0.3559322033898305</v>
+        <v>0.37906137184115524</v>
       </c>
       <c r="C36" s="37">
-        <v>0.35775719483956336</v>
+        <v>0.3811319424866084</v>
       </c>
       <c r="D36" s="37">
-        <v>0.35830807493738404</v>
+        <v>0.3817586245734857</v>
       </c>
       <c r="E36" s="37">
-        <v>0.3585692855803488</v>
+        <v>0.38205457351641053</v>
       </c>
       <c r="F36" s="37">
-        <v>0.35818859689006094</v>
+        <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B37" s="37">
-        <v>0.0211864406779661</v>
+        <v>0.02256317689530686</v>
       </c>
       <c r="C37" s="37">
-        <v>0.016539861065167052</v>
+        <v>0.017620524386805753</v>
       </c>
       <c r="D37" s="37">
-        <v>0.015352425902612982</v>
+        <v>0.016357211590813603</v>
       </c>
       <c r="E37" s="37">
-        <v>0.015000937558597412</v>
+        <v>0.015983457121878854</v>
       </c>
       <c r="F37" s="37">
-        <v>0.01636810039101573</v>
+        <v>0.017438987763643585</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3326,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="10">
-        <v>549850</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -3260,7 +3334,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="11">
-        <v>323002</v>
+        <v>282277</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3268,7 +3342,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="12">
-        <v>0.5874365736109848</v>
+        <v>0.5469583498842245</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -3276,7 +3350,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="13">
-        <v>58.71053745239103</v>
+        <v>48.44287620611784</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -501,7 +501,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -577,6 +577,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -595,7 +605,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -614,11 +624,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -651,6 +666,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -669,7 +693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -690,11 +714,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -704,13 +729,14 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,7 +1306,7 @@
       <c r="A32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="24" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1310,22 +1336,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1333,23 +1359,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
@@ -1368,23 +1394,23 @@
       <c r="A4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>12000*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>12360*Assumptions!B23</f>
         <v>222480</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>12731*Assumptions!B24</f>
         <v>280082</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>13113*Assumptions!B25</f>
         <v>327825</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>13506*Assumptions!B26</f>
         <v>337650</v>
       </c>
@@ -1393,23 +1419,23 @@
       <c r="A5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>250*Assumptions!B22</f>
         <v>3000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>250*Assumptions!B23</f>
         <v>4500</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>250*Assumptions!B24</f>
         <v>5500</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>250*Assumptions!B25</f>
         <v>6250</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>250*Assumptions!B26</f>
         <v>6250</v>
       </c>
@@ -1418,23 +1444,23 @@
       <c r="A6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>SUM(B4:B5)</f>
         <v>147000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>SUM(C4:C5)</f>
         <v>226980</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>SUM(D4:D5)</f>
         <v>285582</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>SUM(E4:E5)</f>
         <v>334075</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>SUM(F4:F5)</f>
         <v>343900</v>
       </c>
@@ -1453,23 +1479,23 @@
       <c r="A8" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>-B4*0.1</f>
         <v>-14400</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>-C4*0.1</f>
         <v>-22248</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>-D4*0.1</f>
         <v>-28008.2</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>-E4*0.1</f>
         <v>-32782.5</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>-F4*0.1</f>
         <v>-33765</v>
       </c>
@@ -1478,23 +1504,23 @@
       <c r="A9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <f>SUM(B8:B8)</f>
         <v>-14400</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>SUM(C8:C8)</f>
         <v>-22248</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>SUM(D8:D8)</f>
         <v>-28008</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>SUM(E8:E8)</f>
         <v>-32782</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <f>SUM(F8:F8)</f>
         <v>-33765</v>
       </c>
@@ -1513,23 +1539,23 @@
       <c r="A11" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>7000*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>7210*Assumptions!B23</f>
         <v>129780</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>7426*Assumptions!B24</f>
         <v>163372</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>7649*Assumptions!B25</f>
         <v>191225</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>7878*Assumptions!B26</f>
         <v>196950</v>
       </c>
@@ -1538,23 +1564,23 @@
       <c r="A12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUM(B11:B11)</f>
         <v>84000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>SUM(C11:C11)</f>
         <v>129780</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>SUM(D11:D11)</f>
         <v>163372</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>SUM(E11:E11)</f>
         <v>191225</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>SUM(F11:F11)</f>
         <v>196950</v>
       </c>
@@ -1573,19 +1599,19 @@
       <c r="A14" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <v>5000</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <v>6000</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>7000</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>8000</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <v>9000</v>
       </c>
     </row>
@@ -1593,23 +1619,23 @@
       <c r="A15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="27" t="str">
+      <c r="B15" s="28" t="str">
         <f>SUM(B14:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="27" t="str">
+      <c r="C15" s="28" t="str">
         <f>SUM(C14:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="27" t="str">
+      <c r="D15" s="28" t="str">
         <f>SUM(D14:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="27" t="str">
+      <c r="E15" s="28" t="str">
         <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="27" t="str">
+      <c r="F15" s="28" t="str">
         <f>SUM(F14:F14)</f>
         <v>0</v>
       </c>
@@ -1618,23 +1644,23 @@
       <c r="A17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>B6+B9+B12+B15</f>
         <v>221600</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C6+C9+C12+C15</f>
         <v>340512</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D6+D9+D12+D15</f>
         <v>427946</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E6+E9+E12+E15</f>
         <v>500518</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>F6+F9+F12+F15</f>
         <v>516085</v>
       </c>
@@ -1674,28 +1700,28 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1709,19 +1735,19 @@
       <c r="C4" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>55000</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>0.2</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>70207.5</v>
       </c>
     </row>
@@ -1735,19 +1761,19 @@
       <c r="C5" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>1</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>45000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>0.2</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <v>57442.5</v>
       </c>
     </row>
@@ -1761,19 +1787,19 @@
       <c r="C6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>0.5</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>28000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <v>15071</v>
       </c>
     </row>
@@ -1793,7 +1819,7 @@
       <c r="A9" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="33">
         <v>3</v>
       </c>
     </row>
@@ -1801,7 +1827,7 @@
       <c r="A10" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="33">
         <v>2.5</v>
       </c>
     </row>
@@ -1809,7 +1835,7 @@
       <c r="A11" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>114000</v>
       </c>
     </row>
@@ -1817,7 +1843,7 @@
       <c r="A12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>20000</v>
       </c>
     </row>
@@ -1825,7 +1851,7 @@
       <c r="A13" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>8721</v>
       </c>
     </row>
@@ -1833,15 +1859,15 @@
       <c r="A14" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <v>142721</v>
       </c>
     </row>
@@ -1856,22 +1882,22 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1879,19 +1905,19 @@
       <c r="A19" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <v>142721</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <v>142721</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <v>142721</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <v>142721</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="27">
         <v>142721</v>
       </c>
     </row>
@@ -1899,23 +1925,23 @@
       <c r="A20" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="34">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="34">
         <f>(1+Assumptions!B29)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="34">
         <f>(1+Assumptions!B29)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="34">
         <f>(1+Assumptions!B29)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="34">
         <f>(1+Assumptions!B29)^4</f>
         <v>1.1255088100000001</v>
       </c>
@@ -1924,20 +1950,20 @@
       <c r="A21" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="35">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="35">
         <v>1</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="35">
         <v>1</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="35">
         <v>1</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="35">
         <v>1</v>
       </c>
     </row>
@@ -1945,23 +1971,23 @@
       <c r="A22" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>B19*B20*B21</f>
         <v>118934</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>C19*C20*C21</f>
         <v>147003</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>D19*D20*D21</f>
         <v>151413</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>E19*E20*E21</f>
         <v>155955</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="28">
         <f>F19*F20*F21</f>
         <v>160634</v>
       </c>
@@ -1992,22 +2018,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2015,23 +2041,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
@@ -2050,23 +2076,23 @@
       <c r="A4" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>500*Assumptions!B22</f>
         <v>6000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>515*Assumptions!B23</f>
         <v>9270</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>530*Assumptions!B24</f>
         <v>11660</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>546*Assumptions!B25</f>
         <v>13650</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>562*Assumptions!B26</f>
         <v>14050</v>
       </c>
@@ -2075,23 +2101,23 @@
       <c r="A5" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B4:B4)</f>
         <v>6000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C4:C4)</f>
         <v>9270</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D4:D4)</f>
         <v>11660</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E4:E4)</f>
         <v>13650</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F4:F4)</f>
         <v>14050</v>
       </c>
@@ -2110,23 +2136,23 @@
       <c r="A7" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>300*Assumptions!B22</f>
         <v>3600</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>309*Assumptions!B23</f>
         <v>5562</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>318*Assumptions!B24</f>
         <v>6996</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>328*Assumptions!B25</f>
         <v>8200</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>338*Assumptions!B26</f>
         <v>8450</v>
       </c>
@@ -2135,23 +2161,23 @@
       <c r="A8" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(B7:B7)</f>
         <v>3600</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>SUM(C7:C7)</f>
         <v>5562</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>SUM(D7:D7)</f>
         <v>6996</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>SUM(E7:E7)</f>
         <v>8200</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>SUM(F7:F7)</f>
         <v>8450</v>
       </c>
@@ -2170,23 +2196,23 @@
       <c r="A10" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>2814*12</f>
         <v>33768</v>
       </c>
@@ -2195,23 +2221,23 @@
       <c r="A11" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>300*12</f>
         <v>3600</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>308*12</f>
         <v>3696</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>316*12</f>
         <v>3792</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>324*12</f>
         <v>3888</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>332*12</f>
         <v>3984</v>
       </c>
@@ -2220,19 +2246,19 @@
       <c r="A12" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>2400</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>2460</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>2522</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>2585</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <v>2650</v>
       </c>
     </row>
@@ -2240,23 +2266,23 @@
       <c r="A13" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>SUM(B10:B12)</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>SUM(C10:C12)</f>
         <v>37056</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>SUM(D10:D12)</f>
         <v>38138</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>SUM(E10:E12)</f>
         <v>39257</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <f>SUM(F10:F12)</f>
         <v>40402</v>
       </c>
@@ -2275,19 +2301,19 @@
       <c r="A15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <v>3000</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <v>3075</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <v>3152</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <v>3231</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <v>3312</v>
       </c>
     </row>
@@ -2295,23 +2321,23 @@
       <c r="A16" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>SUM(B15:B15)</f>
         <v>3000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>SUM(C15:C15)</f>
         <v>3075</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>SUM(D15:D15)</f>
         <v>3152</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>SUM(E15:E15)</f>
         <v>3231</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>SUM(F15:F15)</f>
         <v>3312</v>
       </c>
@@ -2320,23 +2346,23 @@
       <c r="A18" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="28">
         <f>B5+B8+B13+B16</f>
         <v>48600</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>C5+C8+C13+C16</f>
         <v>54963</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>D5+D8+D13+D16</f>
         <v>59946</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>E5+E8+E13+E16</f>
         <v>64338</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <f>F5+F8+F13+F16</f>
         <v>66214</v>
       </c>
@@ -2364,22 +2390,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2397,19 +2423,19 @@
       <c r="A3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <v>6959.808550594178</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <v>6959.808550594178</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <v>6959.808550594178</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <v>6959.808550594178</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <v>6959.808550594178</v>
       </c>
     </row>
@@ -2417,23 +2443,23 @@
       <c r="A4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="28">
         <f>SUM(B3:B3)</f>
         <v>6960</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <f>SUM(C3:C3)</f>
         <v>6960</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="28">
         <f>SUM(D3:D3)</f>
         <v>6960</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <f>SUM(E3:E3)</f>
         <v>6960</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <f>SUM(F3:F3)</f>
         <v>6960</v>
       </c>
@@ -2461,22 +2487,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2484,23 +2510,23 @@
       <c r="A2" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>'Revenue Schedule'!B17</f>
         <v>221600</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Revenue Schedule'!C17</f>
         <v>340512</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Revenue Schedule'!D17</f>
         <v>427946</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Revenue Schedule'!E17</f>
         <v>500518</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Revenue Schedule'!F17</f>
         <v>516085</v>
       </c>
@@ -2509,23 +2535,23 @@
       <c r="A3" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>'Staffing &amp; Personnel'!B22</f>
         <v>118934</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>'Staffing &amp; Personnel'!C22</f>
         <v>147003</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>'Staffing &amp; Personnel'!D22</f>
         <v>151413</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>'Staffing &amp; Personnel'!E22</f>
         <v>155955</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>'Staffing &amp; Personnel'!F22</f>
         <v>160634</v>
       </c>
@@ -2534,23 +2560,23 @@
       <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>'Operating Expenses'!B18</f>
         <v>48600</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>'Operating Expenses'!C18</f>
         <v>54963</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'Operating Expenses'!D18</f>
         <v>59946</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'Operating Expenses'!E18</f>
         <v>64338</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'Operating Expenses'!F18</f>
         <v>66214</v>
       </c>
@@ -2559,23 +2585,23 @@
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>'Capital &amp; Debt'!B4</f>
         <v>6960</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Capital &amp; Debt'!C4</f>
         <v>6960</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Capital &amp; Debt'!D4</f>
         <v>6960</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Capital &amp; Debt'!E4</f>
         <v>6960</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>'Capital &amp; Debt'!F4</f>
         <v>6960</v>
       </c>
@@ -2584,23 +2610,23 @@
       <c r="A6" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>B3+B4+B5</f>
         <v>174494</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>C3+C4+C5</f>
         <v>208926</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>D3+D4+D5</f>
         <v>218319</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>E3+E4+E5</f>
         <v>227253</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>F3+F4+F5</f>
         <v>233808</v>
       </c>
@@ -2609,23 +2635,23 @@
       <c r="A7" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>B2-B6</f>
         <v>47106</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C2-C6</f>
         <v>131586</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>D2-D6</f>
         <v>209627</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E2-E6</f>
         <v>273265</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>F2-F6</f>
         <v>282277</v>
       </c>
@@ -2634,23 +2660,23 @@
       <c r="A8" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>B7</f>
         <v>47106</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>178692</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>388319</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>661584</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>943861</v>
       </c>
@@ -2659,23 +2685,23 @@
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="36">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="36">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="36">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="36">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="36">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
       </c>
@@ -2703,17 +2729,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2731,7 +2757,7 @@
       <c r="A5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2739,7 +2765,7 @@
       <c r="A6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="33" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2747,7 +2773,7 @@
       <c r="A7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2755,7 +2781,7 @@
       <c r="A8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="33" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2763,7 +2789,7 @@
       <c r="A9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2771,7 +2797,7 @@
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="33" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2779,7 +2805,7 @@
       <c r="A11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2787,7 +2813,7 @@
       <c r="A12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="33" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2802,22 +2828,22 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2825,23 +2851,23 @@
       <c r="A16" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>'Revenue Schedule'!B2</f>
         <v>12</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Revenue Schedule'!C2</f>
         <v>18</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Revenue Schedule'!D2</f>
         <v>22</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Revenue Schedule'!E2</f>
         <v>25</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Revenue Schedule'!F2</f>
         <v>25</v>
       </c>
@@ -2853,40 +2879,40 @@
       <c r="B17" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="39">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="39">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="39">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F17" s="37" t="str">
+      <c r="F17" s="39" t="str">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2894,23 +2920,23 @@
       <c r="A20" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>'Financial Model'!B2</f>
         <v>221600</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>'Financial Model'!C2</f>
         <v>340512</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>'Financial Model'!D2</f>
         <v>427946</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>'Financial Model'!E2</f>
         <v>500518</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>'Financial Model'!F2</f>
         <v>516085</v>
       </c>
@@ -2919,23 +2945,23 @@
       <c r="A21" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>'Financial Model'!B3</f>
         <v>118934</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>'Financial Model'!C3</f>
         <v>147003</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>'Financial Model'!D3</f>
         <v>151413</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>'Financial Model'!E3</f>
         <v>155955</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>'Financial Model'!F3</f>
         <v>160634</v>
       </c>
@@ -2944,23 +2970,23 @@
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>'Financial Model'!B4</f>
         <v>48600</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>'Financial Model'!C4</f>
         <v>54963</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>'Financial Model'!D4</f>
         <v>59946</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>'Financial Model'!E4</f>
         <v>64338</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>'Financial Model'!F4</f>
         <v>66214</v>
       </c>
@@ -2969,48 +2995,48 @@
       <c r="A23" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>'Financial Model'!B6</f>
         <v>174494</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>'Financial Model'!C6</f>
         <v>208926</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>'Financial Model'!D6</f>
         <v>218319</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>'Financial Model'!E6</f>
         <v>227253</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f>'Financial Model'!F6</f>
         <v>233808</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="40">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="40">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="40">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="40">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="40">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
@@ -3019,29 +3045,29 @@
       <c r="A25" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>'Financial Model'!B8</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>'Financial Model'!C8</f>
         <v>178692</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>'Financial Model'!D8</f>
         <v>388319</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>'Financial Model'!E8</f>
         <v>661584</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>'Financial Model'!F8</f>
         <v>943861</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="13">
@@ -3079,23 +3105,23 @@
       <c r="A29" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>18466.666666666668</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>18917.333333333332</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>19452.090909090908</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>20020.72</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="27">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>20643.4</v>
       </c>
@@ -3104,23 +3130,23 @@
       <c r="A30" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="39">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="39">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="39">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="39">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="39">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.3112549289361249</v>
       </c>
@@ -3129,29 +3155,29 @@
       <c r="A31" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="39">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="39">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="39">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="39">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="33" t="s">
         <v>146</v>
       </c>
       <c r="B32" s="12">
@@ -3189,19 +3215,19 @@
       <c r="A35" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="39">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="39">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="39">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="39">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="39">
         <v>0.6009378300086227</v>
       </c>
     </row>
@@ -3209,19 +3235,19 @@
       <c r="A36" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="39">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="39">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="39">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="39">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="39">
         <v>0.3816231822277338</v>
       </c>
     </row>
@@ -3229,19 +3255,19 @@
       <c r="A37" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="39">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="39">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="39">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E37" s="37">
+      <c r="E37" s="39">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="39">
         <v>0.017438987763643585</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="152">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -105,6 +105,12 @@
     <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
     <t>SCHOOL INFORMATION</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
   </si>
   <si>
     <t>5 Years</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Year 1</t>
@@ -501,7 +504,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -574,6 +577,12 @@
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -693,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -713,28 +722,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1092,222 +1103,230 @@
       </c>
       <c r="B1" s="18"/>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="22">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="22">
         <v>25</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="20">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="20">
-        <v>25</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>39</v>
+      <c r="A13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>42</v>
+      <c r="A15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>44</v>
+      <c r="A16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>46</v>
+      <c r="A17" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>48</v>
+      <c r="A18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>50</v>
+      <c r="A19" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="23">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="23">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="23">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="23">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="23">
         <v>25</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="22">
+      <c r="A29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="24">
         <v>0.03</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="22">
+      <c r="A30" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="24">
         <v>0.025</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>62</v>
+      <c r="A32" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1336,53 +1355,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1391,83 +1410,83 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="29">
         <f>12000*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>12360*Assumptions!B23</f>
         <v>222480</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>12731*Assumptions!B24</f>
         <v>280082</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>13113*Assumptions!B25</f>
         <v>327825</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>13506*Assumptions!B26</f>
         <v>337650</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="29">
         <f>250*Assumptions!B22</f>
         <v>3000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>250*Assumptions!B23</f>
         <v>4500</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>250*Assumptions!B24</f>
         <v>5500</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>250*Assumptions!B25</f>
         <v>6250</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>250*Assumptions!B26</f>
         <v>6250</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="28">
+        <v>74</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B4:B5)</f>
         <v>147000</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>SUM(C4:C5)</f>
         <v>226980</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>SUM(D4:D5)</f>
         <v>285582</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>SUM(E4:E5)</f>
         <v>334075</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>SUM(F4:F5)</f>
         <v>343900</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1476,58 +1495,58 @@
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="29">
         <f>-B4*0.1</f>
         <v>-14400</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>-C4*0.1</f>
         <v>-22248</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>-D4*0.1</f>
         <v>-28008.2</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>-E4*0.1</f>
         <v>-32782.5</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>-F4*0.1</f>
         <v>-33765</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="28">
+        <v>77</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>-14400</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>-22248</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>-28008</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>-32782</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>-33765</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1536,58 +1555,58 @@
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="29">
         <f>7000*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>7210*Assumptions!B23</f>
         <v>129780</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>7426*Assumptions!B24</f>
         <v>163372</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>7649*Assumptions!B25</f>
         <v>191225</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>7878*Assumptions!B26</f>
         <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="28">
+        <v>80</v>
+      </c>
+      <c r="B12" s="30">
         <f>SUM(B11:B11)</f>
         <v>84000</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="30">
         <f>SUM(C11:C11)</f>
         <v>129780</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="30">
         <f>SUM(D11:D11)</f>
         <v>163372</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="30">
         <f>SUM(E11:E11)</f>
         <v>191225</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="30">
         <f>SUM(F11:F11)</f>
         <v>196950</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1596,71 +1615,71 @@
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="A14" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="29">
         <v>5000</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="29">
         <v>6000</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="29">
         <v>7000</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="29">
         <v>8000</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="29">
         <v>9000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="28" t="str">
+        <v>83</v>
+      </c>
+      <c r="B15" s="30" t="str">
         <f>SUM(B14:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="28" t="str">
+      <c r="C15" s="30" t="str">
         <f>SUM(C14:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="28" t="str">
+      <c r="D15" s="30" t="str">
         <f>SUM(D14:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="28" t="str">
+      <c r="E15" s="30" t="str">
         <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="28" t="str">
+      <c r="F15" s="30" t="str">
         <f>SUM(F14:F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="28">
+        <v>84</v>
+      </c>
+      <c r="B17" s="30">
         <f>B6+B9+B12+B15</f>
         <v>221600</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="30">
         <f>C6+C9+C12+C15</f>
         <v>340512</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="30">
         <f>D6+D9+D12+D15</f>
         <v>427946</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="30">
         <f>E6+E9+E12+E15</f>
         <v>500518</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="30">
         <f>F6+F9+F12+F15</f>
         <v>516085</v>
       </c>
@@ -1689,7 +1708,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1700,51 +1719,51 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="27" t="s">
         <v>92</v>
       </c>
+      <c r="H3" s="27" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="29">
+      <c r="C4" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>55000</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="24">
         <v>0.2</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="24">
         <v>0.0765</v>
       </c>
       <c r="H4" s="32">
@@ -1752,25 +1771,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>45000</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="24">
         <v>0.2</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="24">
         <v>0.0765</v>
       </c>
       <c r="H5" s="32">
@@ -1778,25 +1797,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="29">
+      <c r="C6" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="25">
         <v>0.5</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>28000</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="24">
         <v>0</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="24">
         <v>0.0765</v>
       </c>
       <c r="H6" s="32">
@@ -1805,7 +1824,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1816,64 +1835,64 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>101</v>
+      <c r="A9" s="21" t="s">
+        <v>102</v>
       </c>
       <c r="B9" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>102</v>
+      <c r="A10" s="21" t="s">
+        <v>103</v>
       </c>
       <c r="B10" s="33">
         <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="34">
         <v>114000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="30">
+      <c r="A12" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="34">
         <v>20000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="30">
+      <c r="A13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="34">
         <v>8721</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="A14" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="32">
+        <v>108</v>
+      </c>
+      <c r="B15" s="35">
         <v>142721</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1882,112 +1901,112 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="25" t="s">
+      <c r="A18" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="D18" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="E18" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F18" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="27">
+      <c r="A19" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="29">
         <v>142721</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="29">
         <v>142721</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="29">
         <v>142721</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="29">
         <v>142721</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="29">
         <v>142721</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="34">
+      <c r="A20" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="36">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="36">
         <f>(1+Assumptions!B29)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="36">
         <f>(1+Assumptions!B29)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="36">
         <f>(1+Assumptions!B29)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="36">
         <f>(1+Assumptions!B29)^4</f>
         <v>1.1255088100000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="35">
+      <c r="A21" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="37">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="37">
         <v>1</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="37">
         <v>1</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="37">
         <v>1</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="28">
+        <v>113</v>
+      </c>
+      <c r="B22" s="30">
         <f>B19*B20*B21</f>
         <v>118934</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="30">
         <f>C19*C20*C21</f>
         <v>147003</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="30">
         <f>D19*D20*D21</f>
         <v>151413</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="30">
         <f>E19*E20*E21</f>
         <v>155955</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="30">
         <f>F19*F20*F21</f>
         <v>160634</v>
       </c>
@@ -2018,53 +2037,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2073,58 +2092,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="29">
         <f>500*Assumptions!B22</f>
         <v>6000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>515*Assumptions!B23</f>
         <v>9270</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>530*Assumptions!B24</f>
         <v>11660</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>546*Assumptions!B25</f>
         <v>13650</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>562*Assumptions!B26</f>
         <v>14050</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="28">
+        <v>116</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B4:B4)</f>
         <v>6000</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C4:C4)</f>
         <v>9270</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D4:D4)</f>
         <v>11660</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E4:E4)</f>
         <v>13650</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F4:F4)</f>
         <v>14050</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2133,58 +2152,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="29">
         <f>300*Assumptions!B22</f>
         <v>3600</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <f>309*Assumptions!B23</f>
         <v>5562</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>318*Assumptions!B24</f>
         <v>6996</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <f>328*Assumptions!B25</f>
         <v>8200</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <f>338*Assumptions!B26</f>
         <v>8450</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="28">
+        <v>119</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B7:B7)</f>
         <v>3600</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>SUM(C7:C7)</f>
         <v>5562</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>SUM(D7:D7)</f>
         <v>6996</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>SUM(E7:E7)</f>
         <v>8200</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="30">
         <f>SUM(F7:F7)</f>
         <v>8450</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2193,103 +2212,103 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="29">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>2814*12</f>
         <v>33768</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="29">
         <f>300*12</f>
         <v>3600</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>308*12</f>
         <v>3696</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>316*12</f>
         <v>3792</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>324*12</f>
         <v>3888</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>332*12</f>
         <v>3984</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="29">
         <v>2400</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <v>2460</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <v>2522</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <v>2585</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>2650</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="28">
+        <v>124</v>
+      </c>
+      <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="30">
         <f>SUM(C10:C12)</f>
         <v>37056</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="30">
         <f>SUM(D10:D12)</f>
         <v>38138</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="30">
         <f>SUM(E10:E12)</f>
         <v>39257</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="30">
         <f>SUM(F10:F12)</f>
         <v>40402</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2298,71 +2317,71 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="A15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="29">
         <v>3000</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="29">
         <v>3075</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="29">
         <v>3152</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="29">
         <v>3231</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="29">
         <v>3312</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="28">
+        <v>127</v>
+      </c>
+      <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
         <v>3000</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="30">
         <f>SUM(C15:C15)</f>
         <v>3075</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="30">
         <f>SUM(D15:D15)</f>
         <v>3152</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="30">
         <f>SUM(E15:E15)</f>
         <v>3231</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="30">
         <f>SUM(F15:F15)</f>
         <v>3312</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" s="28">
+        <v>128</v>
+      </c>
+      <c r="B18" s="30">
         <f>B5+B8+B13+B16</f>
         <v>48600</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="30">
         <f>C5+C8+C13+C16</f>
         <v>54963</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="30">
         <f>D5+D8+D13+D16</f>
         <v>59946</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="30">
         <f>E5+E8+E13+E16</f>
         <v>64338</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="30">
         <f>F5+F8+F13+F16</f>
         <v>66214</v>
       </c>
@@ -2390,28 +2409,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2420,46 +2439,46 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="29">
         <v>6959.808550594178</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <v>6959.808550594178</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <v>6959.808550594178</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <v>6959.808550594178</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="28">
+        <v>131</v>
+      </c>
+      <c r="B4" s="30">
         <f>SUM(B3:B3)</f>
         <v>6960</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="30">
         <f>SUM(C3:C3)</f>
         <v>6960</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="30">
         <f>SUM(D3:D3)</f>
         <v>6960</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="30">
         <f>SUM(E3:E3)</f>
         <v>6960</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="30">
         <f>SUM(F3:F3)</f>
         <v>6960</v>
       </c>
@@ -2487,221 +2506,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="29">
         <f>'Revenue Schedule'!B17</f>
         <v>221600</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="29">
         <f>'Revenue Schedule'!C17</f>
         <v>340512</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="29">
         <f>'Revenue Schedule'!D17</f>
         <v>427946</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="29">
         <f>'Revenue Schedule'!E17</f>
         <v>500518</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="29">
         <f>'Revenue Schedule'!F17</f>
         <v>516085</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="29">
         <f>'Staffing &amp; Personnel'!B22</f>
         <v>118934</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <f>'Staffing &amp; Personnel'!C22</f>
         <v>147003</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <f>'Staffing &amp; Personnel'!D22</f>
         <v>151413</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <f>'Staffing &amp; Personnel'!E22</f>
         <v>155955</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <f>'Staffing &amp; Personnel'!F22</f>
         <v>160634</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="29">
         <f>'Operating Expenses'!B18</f>
         <v>48600</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>'Operating Expenses'!C18</f>
         <v>54963</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>'Operating Expenses'!D18</f>
         <v>59946</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>'Operating Expenses'!E18</f>
         <v>64338</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>'Operating Expenses'!F18</f>
         <v>66214</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <f>'Capital &amp; Debt'!B4</f>
         <v>6960</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Capital &amp; Debt'!C4</f>
         <v>6960</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>'Capital &amp; Debt'!D4</f>
         <v>6960</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>'Capital &amp; Debt'!E4</f>
         <v>6960</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>'Capital &amp; Debt'!F4</f>
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="28">
+        <v>134</v>
+      </c>
+      <c r="B6" s="30">
         <f>B3+B4+B5</f>
         <v>174494</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>C3+C4+C5</f>
         <v>208926</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>D3+D4+D5</f>
         <v>218319</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>E3+E4+E5</f>
         <v>227253</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>F3+F4+F5</f>
         <v>233808</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="28">
+        <v>135</v>
+      </c>
+      <c r="B7" s="30">
         <f>B2-B6</f>
         <v>47106</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>C2-C6</f>
         <v>131586</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>D2-D6</f>
         <v>209627</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>E2-E6</f>
         <v>273265</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>F2-F6</f>
         <v>282277</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="29">
         <f>B7</f>
         <v>47106</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>B8+C7</f>
         <v>178692</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>C8+D7</f>
         <v>388319</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>D8+E7</f>
         <v>661584</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>E8+F7</f>
         <v>943861</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="38">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="38">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="38">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="38">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
       </c>
@@ -2729,23 +2748,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="A1" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>137</v>
+      <c r="A2" s="40" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2754,72 +2773,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>24</v>
+      <c r="A5" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>38</v>
+      <c r="A11" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="B12" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2828,240 +2847,240 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F15" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="28">
         <f>'Revenue Schedule'!B2</f>
         <v>12</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="28">
         <f>'Revenue Schedule'!C2</f>
         <v>18</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="28">
         <f>'Revenue Schedule'!D2</f>
         <v>22</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="28">
         <f>'Revenue Schedule'!E2</f>
         <v>25</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="28">
         <f>'Revenue Schedule'!F2</f>
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>140</v>
+      <c r="A17" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="39">
+        <v>142</v>
+      </c>
+      <c r="C17" s="41">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="41">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="41">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F17" s="39" t="str">
+      <c r="F17" s="41" t="str">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="25" t="s">
+      <c r="A19" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="E19" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F19" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="29">
         <f>'Financial Model'!B2</f>
         <v>221600</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="29">
         <f>'Financial Model'!C2</f>
         <v>340512</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>'Financial Model'!D2</f>
         <v>427946</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>'Financial Model'!E2</f>
         <v>500518</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="29">
         <f>'Financial Model'!F2</f>
         <v>516085</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="29">
         <f>'Financial Model'!B3</f>
         <v>118934</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="29">
         <f>'Financial Model'!C3</f>
         <v>147003</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="29">
         <f>'Financial Model'!D3</f>
         <v>151413</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="29">
         <f>'Financial Model'!E3</f>
         <v>155955</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="29">
         <f>'Financial Model'!F3</f>
         <v>160634</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="29">
         <f>'Financial Model'!B4</f>
         <v>48600</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="29">
         <f>'Financial Model'!C4</f>
         <v>54963</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <f>'Financial Model'!D4</f>
         <v>59946</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="29">
         <f>'Financial Model'!E4</f>
         <v>64338</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="29">
         <f>'Financial Model'!F4</f>
         <v>66214</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="28">
+        <v>134</v>
+      </c>
+      <c r="B23" s="30">
         <f>'Financial Model'!B6</f>
         <v>174494</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>'Financial Model'!C6</f>
         <v>208926</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="30">
         <f>'Financial Model'!D6</f>
         <v>218319</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="30">
         <f>'Financial Model'!E6</f>
         <v>227253</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="30">
         <f>'Financial Model'!F6</f>
         <v>233808</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="40">
+        <v>135</v>
+      </c>
+      <c r="B24" s="42">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="42">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="42">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="42">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="42">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="29">
         <f>'Financial Model'!B8</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="29">
         <f>'Financial Model'!C8</f>
         <v>178692</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <f>'Financial Model'!D8</f>
         <v>388319</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <f>'Financial Model'!E8</f>
         <v>661584</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="29">
         <f>'Financial Model'!F8</f>
         <v>943861</v>
       </c>
@@ -3093,7 +3112,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3102,83 +3121,83 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="27">
+      <c r="A29" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="29">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>18466.666666666668</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>18917.333333333332</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="29">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>19452.090909090908</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="29">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>20020.72</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="29">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>20643.4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="39">
+      <c r="A30" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="41">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="41">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="41">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="41">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="41">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" s="39">
+      <c r="A31" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="41">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="41">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="41">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="41">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="41">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3203,7 +3222,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3212,62 +3231,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B35" s="39">
+      <c r="A35" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="41">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="41">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="41">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="41">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="41">
         <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="39">
+      <c r="A36" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="41">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="41">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="41">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="41">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="41">
         <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="39">
+      <c r="A37" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="41">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="41">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="41">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="41">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="41">
         <v>0.017438987763643585</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -14,7 +14,7 @@
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$B32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="153">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -614,7 +617,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -638,11 +641,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -684,6 +692,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -702,7 +719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -724,13 +741,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -747,7 +765,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,7 +1108,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1103,230 +1121,236 @@
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>24</v>
       </c>
+      <c r="D2" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="23">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="23">
         <v>25</v>
       </c>
-      <c r="B3" s="8"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="22">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="22">
-        <v>25</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="22" t="s">
         <v>41</v>
       </c>
+      <c r="B13" s="23" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="22">
+      <c r="A14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
+      <c r="B15" s="23" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="22" t="s">
         <v>46</v>
       </c>
+      <c r="B16" s="23" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="B17" s="23" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="22" t="s">
         <v>50</v>
       </c>
+      <c r="B18" s="23" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="22" t="s">
         <v>52</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="24">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="A23" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="24">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="A24" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="24">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="23">
+      <c r="A25" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="23">
+      <c r="A26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="24">
+      <c r="A29" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="25">
         <v>0.03</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="25">
         <v>0.025</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="25">
+      <c r="A31" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="26">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="22" t="s">
         <v>64</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1355,53 +1379,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1410,83 +1434,83 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="30">
         <f>12000*Assumptions!B22</f>
         <v>144000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>12360*Assumptions!B23</f>
         <v>222480</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>12731*Assumptions!B24</f>
         <v>280082</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>13113*Assumptions!B25</f>
         <v>327825</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>13506*Assumptions!B26</f>
         <v>337650</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="30">
         <f>250*Assumptions!B22</f>
         <v>3000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>250*Assumptions!B23</f>
         <v>4500</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>250*Assumptions!B24</f>
         <v>5500</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>250*Assumptions!B25</f>
         <v>6250</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>250*Assumptions!B26</f>
         <v>6250</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="30">
+        <v>75</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B4:B5)</f>
         <v>147000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C4:C5)</f>
         <v>226980</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D4:D5)</f>
         <v>285582</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E4:E5)</f>
         <v>334075</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F4:F5)</f>
         <v>343900</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1495,58 +1519,58 @@
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="30">
         <f>-B4*0.1</f>
         <v>-14400</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>-C4*0.1</f>
         <v>-22248</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>-D4*0.1</f>
         <v>-28008.2</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>-E4*0.1</f>
         <v>-32782.5</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>-F4*0.1</f>
         <v>-33765</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="30">
+        <v>78</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>-14400</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>-22248</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>-28008</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>-32782</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>-33765</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1555,58 +1579,58 @@
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="30">
         <f>7000*Assumptions!B22</f>
         <v>84000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>7210*Assumptions!B23</f>
         <v>129780</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>7426*Assumptions!B24</f>
         <v>163372</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>7649*Assumptions!B25</f>
         <v>191225</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>7878*Assumptions!B26</f>
         <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="30">
+        <v>81</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B11:B11)</f>
         <v>84000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C11:C11)</f>
         <v>129780</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D11:D11)</f>
         <v>163372</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E11:E11)</f>
         <v>191225</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F11:F11)</f>
         <v>196950</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1615,71 +1639,71 @@
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="A14" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="30">
         <v>5000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>6000</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>7000</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>8000</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>9000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="30" t="str">
+        <v>84</v>
+      </c>
+      <c r="B15" s="31" t="str">
         <f>SUM(B14:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="30" t="str">
+      <c r="C15" s="31" t="str">
         <f>SUM(C14:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="30" t="str">
+      <c r="D15" s="31" t="str">
         <f>SUM(D14:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="30" t="str">
+      <c r="E15" s="31" t="str">
         <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="30" t="str">
+      <c r="F15" s="31" t="str">
         <f>SUM(F14:F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="30">
+        <v>85</v>
+      </c>
+      <c r="B17" s="31">
         <f>B6+B9+B12+B15</f>
         <v>221600</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C6+C9+C12+C15</f>
         <v>340512</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D6+D9+D12+D15</f>
         <v>427946</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E6+E9+E12+E15</f>
         <v>500518</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F6+F9+F12+F15</f>
         <v>516085</v>
       </c>
@@ -1708,7 +1732,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1719,112 +1743,112 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>93</v>
       </c>
+      <c r="H3" s="28" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="25">
+      <c r="C4" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="26">
         <v>1</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>55000</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.2</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="33">
         <v>70207.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>1</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>45000</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>0.2</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="33">
         <v>57442.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="C6" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="26">
         <v>0.5</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <v>28000</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="33">
         <v>15071</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1835,64 +1859,64 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="33">
+      <c r="A9" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="34">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="33">
+      <c r="A10" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="34">
         <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="A11" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="35">
         <v>114000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="34">
+      <c r="A12" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="35">
         <v>20000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="34">
+      <c r="A13" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="35">
         <v>8721</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="34">
+      <c r="A14" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="35">
+      <c r="A15" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="36">
         <v>142721</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1901,112 +1925,112 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="C18" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="D18" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="E18" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F18" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="A19" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="30">
         <v>142721</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>142721</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>142721</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>142721</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>142721</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="36">
+      <c r="A20" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="37">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="37">
         <f>(1+Assumptions!B29)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <f>(1+Assumptions!B29)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="37">
         <f>(1+Assumptions!B29)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="37">
         <f>(1+Assumptions!B29)^4</f>
         <v>1.1255088100000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="37">
+      <c r="A21" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="38">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="38">
         <v>1</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="38">
         <v>1</v>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="38">
         <v>1</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="30">
+        <v>114</v>
+      </c>
+      <c r="B22" s="31">
         <f>B19*B20*B21</f>
         <v>118934</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>C19*C20*C21</f>
         <v>147003</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>D19*D20*D21</f>
         <v>151413</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>E19*E20*E21</f>
         <v>155955</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>F19*F20*F21</f>
         <v>160634</v>
       </c>
@@ -2037,53 +2061,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>12</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>18</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>22</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>25</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2092,58 +2116,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="30">
         <f>500*Assumptions!B22</f>
         <v>6000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>515*Assumptions!B23</f>
         <v>9270</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>530*Assumptions!B24</f>
         <v>11660</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>546*Assumptions!B25</f>
         <v>13650</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>562*Assumptions!B26</f>
         <v>14050</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="30">
+        <v>117</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
         <v>6000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C4:C4)</f>
         <v>9270</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D4:D4)</f>
         <v>11660</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E4:E4)</f>
         <v>13650</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F4:F4)</f>
         <v>14050</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2152,58 +2176,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="29">
+      <c r="A7" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="30">
         <f>300*Assumptions!B22</f>
         <v>3600</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>309*Assumptions!B23</f>
         <v>5562</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>318*Assumptions!B24</f>
         <v>6996</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>328*Assumptions!B25</f>
         <v>8200</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>338*Assumptions!B26</f>
         <v>8450</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="30">
+        <v>120</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
         <v>3600</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C7:C7)</f>
         <v>5562</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D7:D7)</f>
         <v>6996</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E7:E7)</f>
         <v>8200</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F7:F7)</f>
         <v>8450</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2212,103 +2236,103 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="30">
         <f>2500*12</f>
         <v>30000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>2575*12</f>
         <v>30900</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>2652*12</f>
         <v>31824</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>2732*12</f>
         <v>32784</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>2814*12</f>
         <v>33768</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="30">
         <f>300*12</f>
         <v>3600</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>308*12</f>
         <v>3696</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>316*12</f>
         <v>3792</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>324*12</f>
         <v>3888</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>332*12</f>
         <v>3984</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="29">
+      <c r="A12" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="30">
         <v>2400</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>2460</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>2522</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>2585</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>2650</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="30">
+        <v>125</v>
+      </c>
+      <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUM(C10:C12)</f>
         <v>37056</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUM(D10:D12)</f>
         <v>38138</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUM(E10:E12)</f>
         <v>39257</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>SUM(F10:F12)</f>
         <v>40402</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2317,71 +2341,71 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="A15" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="30">
         <v>3000</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>3075</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>3152</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>3231</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>3312</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="30">
+        <v>128</v>
+      </c>
+      <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
         <v>3000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>SUM(C15:C15)</f>
         <v>3075</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>SUM(D15:D15)</f>
         <v>3152</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>SUM(E15:E15)</f>
         <v>3231</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>SUM(F15:F15)</f>
         <v>3312</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="30">
+        <v>129</v>
+      </c>
+      <c r="B18" s="31">
         <f>B5+B8+B13+B16</f>
         <v>48600</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>C5+C8+C13+C16</f>
         <v>54963</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <f>D5+D8+D13+D16</f>
         <v>59946</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <f>E5+E8+E13+E16</f>
         <v>64338</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f>F5+F8+F13+F16</f>
         <v>66214</v>
       </c>
@@ -2409,28 +2433,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2439,46 +2463,46 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="30">
         <v>6959.808550594178</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>6959.808550594178</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <v>6959.808550594178</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <v>6959.808550594178</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="30">
+        <v>132</v>
+      </c>
+      <c r="B4" s="31">
         <f>SUM(B3:B3)</f>
         <v>6960</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <f>SUM(C3:C3)</f>
         <v>6960</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <f>SUM(D3:D3)</f>
         <v>6960</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <f>SUM(E3:E3)</f>
         <v>6960</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <f>SUM(F3:F3)</f>
         <v>6960</v>
       </c>
@@ -2506,221 +2530,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="29">
+      <c r="A2" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="30">
         <f>'Revenue Schedule'!B17</f>
         <v>221600</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <f>'Revenue Schedule'!C17</f>
         <v>340512</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="30">
         <f>'Revenue Schedule'!D17</f>
         <v>427946</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="30">
         <f>'Revenue Schedule'!E17</f>
         <v>500518</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="30">
         <f>'Revenue Schedule'!F17</f>
         <v>516085</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B22</f>
         <v>118934</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <f>'Staffing &amp; Personnel'!C22</f>
         <v>147003</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <f>'Staffing &amp; Personnel'!D22</f>
         <v>151413</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <f>'Staffing &amp; Personnel'!E22</f>
         <v>155955</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <f>'Staffing &amp; Personnel'!F22</f>
         <v>160634</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>'Operating Expenses'!B18</f>
         <v>48600</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>'Operating Expenses'!C18</f>
         <v>54963</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>'Operating Expenses'!D18</f>
         <v>59946</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>'Operating Expenses'!E18</f>
         <v>64338</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>'Operating Expenses'!F18</f>
         <v>66214</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>'Capital &amp; Debt'!B4</f>
         <v>6960</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>'Capital &amp; Debt'!C4</f>
         <v>6960</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>'Capital &amp; Debt'!D4</f>
         <v>6960</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>'Capital &amp; Debt'!E4</f>
         <v>6960</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>'Capital &amp; Debt'!F4</f>
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="30">
+        <v>135</v>
+      </c>
+      <c r="B6" s="31">
         <f>B3+B4+B5</f>
         <v>174494</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C3+C4+C5</f>
         <v>208926</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D3+D4+D5</f>
         <v>218319</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E3+E4+E5</f>
         <v>227253</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F3+F4+F5</f>
         <v>233808</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="30">
+        <v>136</v>
+      </c>
+      <c r="B7" s="31">
         <f>B2-B6</f>
         <v>47106</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C2-C6</f>
         <v>131586</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>D2-D6</f>
         <v>209627</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>E2-E6</f>
         <v>273265</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>F2-F6</f>
         <v>282277</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="30">
         <f>B7</f>
         <v>47106</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>B8+C7</f>
         <v>178692</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>C8+D7</f>
         <v>388319</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>D8+E7</f>
         <v>661584</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>E8+F7</f>
         <v>943861</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="39">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="39">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
       </c>
@@ -2748,23 +2772,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>138</v>
+      <c r="A2" s="41" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2773,72 +2797,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>139</v>
+      <c r="B12" s="34" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2847,246 +2871,246 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="C15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F15" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="28">
+      <c r="A16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>12</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>18</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>22</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>25</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>141</v>
+      <c r="A17" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="41">
+        <v>143</v>
+      </c>
+      <c r="C17" s="42">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F17" s="41" t="str">
+      <c r="F17" s="42" t="str">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F19" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="30">
         <f>'Financial Model'!B2</f>
         <v>221600</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>'Financial Model'!C2</f>
         <v>340512</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>'Financial Model'!D2</f>
         <v>427946</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>'Financial Model'!E2</f>
         <v>500518</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>'Financial Model'!F2</f>
         <v>516085</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="30">
         <f>'Financial Model'!B3</f>
         <v>118934</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>'Financial Model'!C3</f>
         <v>147003</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>'Financial Model'!D3</f>
         <v>151413</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>'Financial Model'!E3</f>
         <v>155955</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>'Financial Model'!F3</f>
         <v>160634</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>'Financial Model'!B4</f>
         <v>48600</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>'Financial Model'!C4</f>
         <v>54963</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>'Financial Model'!D4</f>
         <v>59946</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>'Financial Model'!E4</f>
         <v>64338</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>'Financial Model'!F4</f>
         <v>66214</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="30">
+        <v>135</v>
+      </c>
+      <c r="B23" s="31">
         <f>'Financial Model'!B6</f>
         <v>174494</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>'Financial Model'!C6</f>
         <v>208926</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>'Financial Model'!D6</f>
         <v>218319</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>'Financial Model'!E6</f>
         <v>227253</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>'Financial Model'!F6</f>
         <v>233808</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" s="42">
+      <c r="A24" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="43">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="43">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="43">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="43">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F24" s="42">
+      <c r="F24" s="43">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="30">
         <f>'Financial Model'!B8</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>'Financial Model'!C8</f>
         <v>178692</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>'Financial Model'!D8</f>
         <v>388319</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>'Financial Model'!E8</f>
         <v>661584</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>'Financial Model'!F8</f>
         <v>943861</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="13">
@@ -3112,7 +3136,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3121,83 +3145,83 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="A29" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>18466.666666666668</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>18917.333333333332</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>19452.090909090908</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>20020.72</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>20643.4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="41">
+      <c r="A30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="42">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B31" s="41">
+      <c r="A31" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="42">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="42">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="42">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="42">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>147</v>
+      <c r="A32" s="34" t="s">
+        <v>148</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3222,7 +3246,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3231,62 +3255,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="41">
+      <c r="A35" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="42">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="42">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="42">
         <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="41">
+      <c r="A36" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="42">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="42">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="42">
         <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="41">
+      <c r="A37" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="42">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C37" s="41">
+      <c r="C37" s="42">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="42">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="42">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="42">
         <v>0.017438987763643585</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -12,6 +12,7 @@
     <sheet sheetId="5" name="Capital &amp; Debt" state="visible" r:id="rId9"/>
     <sheet sheetId="6" name="Financial Model" state="visible" r:id="rId10"/>
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
@@ -28,13 +29,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="209">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -493,21 +496,190 @@
   </si>
   <si>
     <t>Philanthropy %</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches profit early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 41.56x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>48.4 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -616,6 +788,24 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -719,7 +909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -766,11 +956,222 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3504,4 +3905,677 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="49">
+        <v>12</v>
+      </c>
+      <c r="D7" s="49">
+        <v>18</v>
+      </c>
+      <c r="E7" s="49">
+        <v>22</v>
+      </c>
+      <c r="F7" s="49">
+        <v>25</v>
+      </c>
+      <c r="G7" s="49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="50">
+        <v>221600</v>
+      </c>
+      <c r="D8" s="50">
+        <v>340512</v>
+      </c>
+      <c r="E8" s="50">
+        <v>427946</v>
+      </c>
+      <c r="F8" s="50">
+        <v>500518</v>
+      </c>
+      <c r="G8" s="50">
+        <v>516085</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="50">
+        <v>118934</v>
+      </c>
+      <c r="D9" s="50">
+        <v>147003</v>
+      </c>
+      <c r="E9" s="50">
+        <v>151413</v>
+      </c>
+      <c r="F9" s="50">
+        <v>155955</v>
+      </c>
+      <c r="G9" s="50">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="50">
+        <v>48600</v>
+      </c>
+      <c r="D10" s="50">
+        <v>54963</v>
+      </c>
+      <c r="E10" s="50">
+        <v>59946</v>
+      </c>
+      <c r="F10" s="50">
+        <v>64338</v>
+      </c>
+      <c r="G10" s="50">
+        <v>66214</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="50">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="D11" s="50">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="E11" s="50">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="F11" s="50">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="G11" s="50">
+        <v>6959.808550594178</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="52">
+        <v>47106</v>
+      </c>
+      <c r="D12" s="52">
+        <v>131586</v>
+      </c>
+      <c r="E12" s="52">
+        <v>209627</v>
+      </c>
+      <c r="F12" s="52">
+        <v>273265</v>
+      </c>
+      <c r="G12" s="52">
+        <v>282277</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="52">
+        <v>47106</v>
+      </c>
+      <c r="D13" s="52">
+        <v>178692</v>
+      </c>
+      <c r="E13" s="52">
+        <v>388319</v>
+      </c>
+      <c r="F13" s="52">
+        <v>661584</v>
+      </c>
+      <c r="G13" s="52">
+        <v>943861</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="53">
+        <v>0.21257220216606498</v>
+      </c>
+      <c r="D14" s="53">
+        <v>0.38643572032703694</v>
+      </c>
+      <c r="E14" s="53">
+        <v>0.4898445130927734</v>
+      </c>
+      <c r="F14" s="53">
+        <v>0.5459643809013862</v>
+      </c>
+      <c r="G14" s="53">
+        <v>0.5469583498842245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="54">
+        <v>18466.666666666668</v>
+      </c>
+      <c r="D15" s="54">
+        <v>18917.333333333332</v>
+      </c>
+      <c r="E15" s="54">
+        <v>19452.090909090908</v>
+      </c>
+      <c r="F15" s="54">
+        <v>20020.72</v>
+      </c>
+      <c r="G15" s="54">
+        <v>20643.4</v>
+      </c>
+      <c r="H15" s="55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="53">
+        <v>0.5367057761732852</v>
+      </c>
+      <c r="D16" s="53">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0.3112549289361249</v>
+      </c>
+      <c r="H16" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="53">
+        <v>0.0657942238267148</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0.04842384409360022</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0.04202352633276161</v>
+      </c>
+      <c r="F17" s="53">
+        <v>0.03856284888855146</v>
+      </c>
+      <c r="G17" s="53">
+        <v>0.038490171192729884</v>
+      </c>
+      <c r="H17" s="55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="53">
+        <v>0.24398014440433213</v>
+      </c>
+      <c r="D18" s="53">
+        <v>0.4068755286157316</v>
+      </c>
+      <c r="E18" s="53">
+        <v>0.5061082473022297</v>
+      </c>
+      <c r="F18" s="53">
+        <v>0.5598699747062044</v>
+      </c>
+      <c r="G18" s="53">
+        <v>0.5604445004214422</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="56">
+        <v>3</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="55" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="57">
+        <v>7.768317132140687</v>
+      </c>
+      <c r="D20" s="57">
+        <v>19.906582055072757</v>
+      </c>
+      <c r="E20" s="57">
+        <v>31.11967785112557</v>
+      </c>
+      <c r="F20" s="57">
+        <v>40.26332017079355</v>
+      </c>
+      <c r="G20" s="57">
+        <v>41.558183374930195</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="55" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="59" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="211">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>Financial Model Summary</t>
@@ -909,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -952,6 +958,12 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -986,9 +998,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2923,7 +2932,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3148,6 +3157,26 @@
       <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3173,18 +3202,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="A1" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
-        <v>139</v>
+      <c r="A2" s="43" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,12 +3287,12 @@
         <v>40</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3318,24 +3347,24 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="42">
+        <v>145</v>
+      </c>
+      <c r="C17" s="44">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="44">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="44">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F17" s="42" t="str">
+      <c r="F17" s="44" t="str">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0</v>
       </c>
@@ -3464,23 +3493,23 @@
       <c r="A24" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="45">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="45">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="45">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="45">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="45">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
@@ -3537,7 +3566,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3547,7 +3576,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
@@ -3572,57 +3601,57 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="42">
+        <v>148</v>
+      </c>
+      <c r="B30" s="44">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="44">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="44">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="44">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="44">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="42">
+        <v>149</v>
+      </c>
+      <c r="B31" s="44">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="44">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="44">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="44">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="44">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3647,7 +3676,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3657,61 +3686,61 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B35" s="42">
+        <v>152</v>
+      </c>
+      <c r="B35" s="44">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="44">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="44">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="44">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="44">
         <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36" s="42">
+        <v>153</v>
+      </c>
+      <c r="B36" s="44">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C36" s="42">
+      <c r="C36" s="44">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="44">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="44">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="44">
         <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="42">
+        <v>154</v>
+      </c>
+      <c r="B37" s="44">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="44">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="44">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="44">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="44">
         <v>0.017438987763643585</v>
       </c>
     </row>
@@ -3924,118 +3953,118 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
+      <c r="B3" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="47" t="s">
+      <c r="B4" s="47" t="s">
         <v>157</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>159</v>
+      <c r="H6" s="50" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="49">
+        <v>162</v>
+      </c>
+      <c r="C7" s="51">
         <v>12</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="51">
         <v>18</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="51">
         <v>22</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="51">
         <v>25</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="51">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="50">
+        <v>163</v>
+      </c>
+      <c r="C8" s="52">
         <v>221600</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="52">
         <v>340512</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="52">
         <v>427946</v>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="52">
         <v>500518</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="52">
         <v>516085</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="50">
+        <v>164</v>
+      </c>
+      <c r="C9" s="52">
         <v>118934</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="52">
         <v>147003</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="52">
         <v>151413</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="52">
         <v>155955</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="52">
         <v>160634</v>
       </c>
     </row>
@@ -4043,419 +4072,419 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="52">
         <v>48600</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="52">
         <v>54963</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="52">
         <v>59946</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="52">
         <v>64338</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="52">
         <v>66214</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="50">
+        <v>165</v>
+      </c>
+      <c r="C11" s="52">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="52">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="52">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="52">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="52">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="52">
+      <c r="B12" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="54">
         <v>47106</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="54">
         <v>131586</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="54">
         <v>209627</v>
       </c>
-      <c r="F12" s="52">
+      <c r="F12" s="54">
         <v>273265</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="54">
         <v>282277</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="52">
+      <c r="B13" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="54">
         <v>47106</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="54">
         <v>178692</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="54">
         <v>388319</v>
       </c>
-      <c r="F13" s="52">
+      <c r="F13" s="54">
         <v>661584</v>
       </c>
-      <c r="G13" s="52">
+      <c r="G13" s="54">
         <v>943861</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="C14" s="53">
+      <c r="B14" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="55">
         <v>0.21257220216606498</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="55">
         <v>0.38643572032703694</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="55">
         <v>0.4898445130927734</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="55">
         <v>0.5459643809013862</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="55">
         <v>0.5469583498842245</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="54">
+      <c r="B15" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="56">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="56">
         <v>18917.333333333332</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="56">
         <v>19452.090909090908</v>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="56">
         <v>20020.72</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="56">
         <v>20643.4</v>
       </c>
-      <c r="H15" s="55" t="s">
-        <v>167</v>
+      <c r="H15" s="57" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="53">
+      <c r="B16" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="55">
         <v>0.5367057761732852</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="55">
         <v>0.43171165773893433</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="55">
         <v>0.3538133315885649</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="55">
         <v>0.31158719566529075</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="55">
         <v>0.3112549289361249</v>
       </c>
-      <c r="H16" s="55" t="s">
-        <v>169</v>
+      <c r="H16" s="57" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="53">
+      <c r="B17" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="55">
         <v>0.0657942238267148</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="55">
         <v>0.04842384409360022</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="55">
         <v>0.04202352633276161</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="55">
         <v>0.03856284888855146</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="55">
         <v>0.038490171192729884</v>
       </c>
-      <c r="H17" s="55" t="s">
-        <v>171</v>
+      <c r="H17" s="57" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="53">
+      <c r="B18" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="55">
         <v>0.24398014440433213</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="55">
         <v>0.4068755286157316</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="55">
         <v>0.5061082473022297</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="55">
         <v>0.5598699747062044</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="55">
         <v>0.5604445004214422</v>
       </c>
-      <c r="H18" s="55" t="s">
-        <v>173</v>
+      <c r="H18" s="57" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="56">
+      <c r="B19" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="58">
         <v>3</v>
       </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="55" t="s">
-        <v>175</v>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="57" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="57">
+      <c r="B20" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="59">
         <v>7.768317132140687</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="59">
         <v>19.906582055072757</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="59">
         <v>31.11967785112557</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="59">
         <v>40.26332017079355</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="59">
         <v>41.558183374930195</v>
       </c>
-      <c r="H20" s="55" t="s">
-        <v>177</v>
+      <c r="H20" s="57" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="58" t="s">
+      <c r="B21" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="55" t="s">
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="57" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="55" t="s">
-        <v>180</v>
+      <c r="B22" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="57" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="61" t="s">
+      <c r="B25" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="C25" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
+      <c r="D25" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="B26" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="C26" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="62" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="B27" s="61" t="s">
         <v>194</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
+      <c r="C27" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="B28" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="C28" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="B29" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
+      <c r="C29" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="B30" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="C30" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="C31" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
+      <c r="B31" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
+      <c r="C31" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
+      <c r="C33" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
+      <c r="B35" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -4594,10 +4594,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="211">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -915,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -995,6 +995,9 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4302,13 +4305,26 @@
       <c r="B21" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="C21" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
+      <c r="C21" s="40" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="60" t="str">
+        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="60" t="str">
+        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="60" t="str">
+        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="60" t="str">
+        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="57" t="s">
         <v>66</v>
       </c>
@@ -4317,13 +4333,13 @@
       <c r="B22" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
       <c r="H22" s="57" t="s">
         <v>182</v>
       </c>
@@ -4346,126 +4362,126 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="62" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="63" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
+      <c r="E25" s="63"/>
+      <c r="F25" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="62" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="D26" s="63" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="E26" s="63"/>
+      <c r="F26" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="62" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="63" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="E27" s="63"/>
+      <c r="F27" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="62" t="s">
         <v>197</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="62" t="s">
+      <c r="D28" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="E28" s="63"/>
+      <c r="F28" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="62" t="s">
         <v>200</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="62" t="s">
+      <c r="D29" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
+      <c r="E29" s="63"/>
+      <c r="F29" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="62" t="s">
         <v>203</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="62" t="s">
+      <c r="D30" s="63" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63" t="s">
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="62" t="s">
         <v>206</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D31" s="62" t="s">
+      <c r="D31" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="62" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="53" t="s">
@@ -4476,22 +4492,21 @@
       <c r="F33" s="53"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -4572,10 +4587,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="211">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -582,10 +582,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -813,7 +813,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,6 +843,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -915,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -992,14 +1002,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4270,10 +4287,18 @@
       <c r="C19" s="58">
         <v>3</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
+      <c r="D19" s="58">
+        <v>3</v>
+      </c>
+      <c r="E19" s="58">
+        <v>3</v>
+      </c>
+      <c r="F19" s="58">
+        <v>3</v>
+      </c>
+      <c r="G19" s="58">
+        <v>3</v>
+      </c>
       <c r="H19" s="57" t="s">
         <v>177</v>
       </c>
@@ -4310,19 +4335,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="60" t="str">
-        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="60" t="str">
-        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="60" t="str">
-        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="60" t="str">
-        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="57" t="s">
@@ -4333,13 +4358,21 @@
       <c r="B22" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="C22" s="61" t="s">
-        <v>182</v>
-      </c>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
+      <c r="C22" s="61">
+        <v>3</v>
+      </c>
+      <c r="D22" s="61">
+        <v>10</v>
+      </c>
+      <c r="E22" s="62">
+        <v>21</v>
+      </c>
+      <c r="F22" s="58">
+        <v>35</v>
+      </c>
+      <c r="G22" s="58">
+        <v>48</v>
+      </c>
       <c r="H22" s="57" t="s">
         <v>182</v>
       </c>
@@ -4362,126 +4395,126 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="63" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
+      <c r="E25" s="64"/>
+      <c r="F25" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="63" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="64" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
+      <c r="E26" s="64"/>
+      <c r="F26" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="63" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
+      <c r="E27" s="64"/>
+      <c r="F27" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="63" t="s">
         <v>197</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
+      <c r="E28" s="64"/>
+      <c r="F28" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="63" t="s">
         <v>200</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64" t="s">
+      <c r="E29" s="64"/>
+      <c r="F29" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="63" t="s">
         <v>203</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="63" t="s">
+      <c r="D30" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="63" t="s">
         <v>206</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
+      <c r="E31" s="64"/>
+      <c r="F31" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="63" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="53" t="s">
@@ -4492,22 +4525,20 @@
       <c r="F33" s="53"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -633,7 +633,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -847,12 +847,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -925,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1002,6 +1002,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1011,10 +1014,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4238,20 +4241,20 @@
       <c r="B17" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="55">
-        <v>0.0657942238267148</v>
+      <c r="C17" s="58">
+        <v>0.1624548736462094</v>
       </c>
       <c r="D17" s="55">
-        <v>0.04842384409360022</v>
+        <v>0.10882435861291231</v>
       </c>
       <c r="E17" s="55">
-        <v>0.04202352633276161</v>
+        <v>0.08912573081650489</v>
       </c>
       <c r="F17" s="55">
-        <v>0.03856284888855146</v>
+        <v>0.07842836821053388</v>
       </c>
       <c r="G17" s="55">
-        <v>0.038490171192729884</v>
+        <v>0.07828025286532257</v>
       </c>
       <c r="H17" s="57" t="s">
         <v>173</v>
@@ -4284,19 +4287,19 @@
       <c r="B19" s="53" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <v>3</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="59">
         <v>3</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="59">
         <v>3</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="59">
         <v>3</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="59">
         <v>3</v>
       </c>
       <c r="H19" s="57" t="s">
@@ -4307,19 +4310,19 @@
       <c r="B20" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="60">
         <v>7.768317132140687</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="60">
         <v>19.906582055072757</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="60">
         <v>31.11967785112557</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F20" s="60">
         <v>40.26332017079355</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G20" s="60">
         <v>41.558183374930195</v>
       </c>
       <c r="H20" s="57" t="s">
@@ -4334,19 +4337,19 @@
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="60" t="str">
+      <c r="D21" s="61" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="60" t="str">
+      <c r="E21" s="61" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="60" t="str">
+      <c r="F21" s="61" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="60" t="str">
+      <c r="G21" s="61" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -4358,19 +4361,19 @@
       <c r="B22" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="C22" s="61">
+      <c r="C22" s="62">
         <v>3</v>
       </c>
-      <c r="D22" s="61">
+      <c r="D22" s="62">
         <v>10</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E22" s="63">
         <v>21</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="59">
         <v>35</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="59">
         <v>48</v>
       </c>
       <c r="H22" s="57" t="s">
@@ -4395,126 +4398,126 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="64" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65" t="s">
+      <c r="E25" s="65"/>
+      <c r="F25" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="64" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="64"/>
-      <c r="F26" s="65" t="s">
+      <c r="E26" s="65"/>
+      <c r="F26" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="64" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65" t="s">
+      <c r="E27" s="65"/>
+      <c r="F27" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="64" t="s">
         <v>197</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="64"/>
-      <c r="F28" s="65" t="s">
+      <c r="E28" s="65"/>
+      <c r="F28" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="64" t="s">
         <v>200</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65" t="s">
+      <c r="E29" s="65"/>
+      <c r="F29" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="64" t="s">
         <v>203</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
+      <c r="E30" s="65"/>
+      <c r="F30" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="64" t="s">
         <v>206</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D31" s="64" t="s">
+      <c r="D31" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="65" t="s">
+      <c r="E31" s="65"/>
+      <c r="F31" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="64" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="53" t="s">
@@ -4525,15 +4528,15 @@
       <c r="F33" s="53"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -507,7 +507,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -2095,25 +2095,25 @@
       <c r="A15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="31" t="str">
+      <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="31" t="str">
+        <v>5000</v>
+      </c>
+      <c r="C15" s="31">
         <f>SUM(C14:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="31" t="str">
+        <v>6000</v>
+      </c>
+      <c r="D15" s="31">
         <f>SUM(D14:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="31" t="str">
+        <v>7000</v>
+      </c>
+      <c r="E15" s="31">
         <f>SUM(E14:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="31" t="str">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="31">
         <f>SUM(F14:F14)</f>
-        <v>0</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="213">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -586,6 +586,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -3965,7 +3971,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4380,170 +4386,191 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="53" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C23" s="59">
+        <v>99</v>
+      </c>
+      <c r="D23" s="59">
+        <v>312</v>
+      </c>
+      <c r="E23" s="59">
+        <v>649</v>
+      </c>
+      <c r="F23" s="59">
+        <v>1063</v>
+      </c>
+      <c r="G23" s="59">
+        <v>1473</v>
+      </c>
+      <c r="H23" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="D25" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="65" t="s">
         <v>191</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>192</v>
       </c>
       <c r="E26" s="65"/>
       <c r="F26" s="66" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G26" s="66"/>
       <c r="H26" s="66"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="65" t="s">
         <v>194</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="65" t="s">
-        <v>195</v>
       </c>
       <c r="E27" s="65"/>
       <c r="F27" s="66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G27" s="66"/>
       <c r="H27" s="66"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="65" t="s">
         <v>197</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>198</v>
       </c>
       <c r="E28" s="65"/>
       <c r="F28" s="66" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="65" t="s">
         <v>200</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="65" t="s">
-        <v>201</v>
       </c>
       <c r="E29" s="65"/>
       <c r="F29" s="66" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G29" s="66"/>
       <c r="H29" s="66"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="64" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="65" t="s">
         <v>203</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>204</v>
       </c>
       <c r="E30" s="65"/>
       <c r="F30" s="66" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G30" s="66"/>
       <c r="H30" s="66"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="64" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="65" t="s">
         <v>206</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="65" t="s">
-        <v>207</v>
       </c>
       <c r="E31" s="65"/>
       <c r="F31" s="66" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G31" s="66"/>
       <c r="H31" s="66"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" s="65"/>
+      <c r="F32" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="67" t="s">
-        <v>210</v>
-      </c>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
+      <c r="C34" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4558,8 +4585,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="218">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -547,6 +547,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -931,7 +946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1008,6 +1023,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3971,7 +3995,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4220,365 +4244,440 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="55">
-        <v>0.5367057761732852</v>
-      </c>
-      <c r="D16" s="55">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E16" s="55">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F16" s="55">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G16" s="55">
-        <v>0.3112549289361249</v>
-      </c>
-      <c r="H16" s="57" t="s">
+      <c r="C16" s="58">
+        <v>14541.150712549514</v>
+      </c>
+      <c r="D16" s="58">
+        <v>11606.989363921899</v>
+      </c>
+      <c r="E16" s="58">
+        <v>9923.582206845189</v>
+      </c>
+      <c r="F16" s="58">
+        <v>9090.112342023767</v>
+      </c>
+      <c r="G16" s="58">
+        <v>9352.312342023766</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="53" t="s">
+      <c r="C17" s="52">
+        <v>500</v>
+      </c>
+      <c r="D17" s="52">
+        <v>515</v>
+      </c>
+      <c r="E17" s="52">
+        <v>530</v>
+      </c>
+      <c r="F17" s="52">
+        <v>546</v>
+      </c>
+      <c r="G17" s="52">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="58">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D17" s="55">
-        <v>0.10882435861291231</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0.08912573081650489</v>
-      </c>
-      <c r="F17" s="55">
-        <v>0.07842836821053388</v>
-      </c>
-      <c r="G17" s="55">
-        <v>0.07828025286532257</v>
-      </c>
-      <c r="H17" s="57" t="s">
+      <c r="C18" s="59">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="59">
+        <v>2058.6666666666665</v>
+      </c>
+      <c r="E18" s="56">
+        <v>1733.6818181818182</v>
+      </c>
+      <c r="F18" s="56">
+        <v>1570.1924</v>
+      </c>
+      <c r="G18" s="56">
+        <v>1615.9705720000002</v>
+      </c>
+      <c r="H18" s="57" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="53" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="C18" s="55">
-        <v>0.24398014440433213</v>
-      </c>
-      <c r="D18" s="55">
-        <v>0.4068755286157316</v>
-      </c>
-      <c r="E18" s="55">
-        <v>0.5061082473022297</v>
-      </c>
-      <c r="F18" s="55">
-        <v>0.5598699747062044</v>
-      </c>
-      <c r="G18" s="55">
-        <v>0.5604445004214422</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="59">
-        <v>3</v>
-      </c>
-      <c r="D19" s="59">
-        <v>3</v>
-      </c>
-      <c r="E19" s="59">
-        <v>3</v>
-      </c>
-      <c r="F19" s="59">
-        <v>3</v>
-      </c>
-      <c r="G19" s="59">
-        <v>3</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>177</v>
+      <c r="C19" s="60">
+        <v>3925.5</v>
+      </c>
+      <c r="D19" s="60">
+        <v>7310.333333333333</v>
+      </c>
+      <c r="E19" s="60">
+        <v>9528.5</v>
+      </c>
+      <c r="F19" s="60">
+        <v>10930.6</v>
+      </c>
+      <c r="G19" s="60">
+        <v>11291.08</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="60">
-        <v>7.768317132140687</v>
-      </c>
-      <c r="D20" s="60">
-        <v>19.906582055072757</v>
-      </c>
-      <c r="E20" s="60">
-        <v>31.11967785112557</v>
-      </c>
-      <c r="F20" s="60">
-        <v>40.26332017079355</v>
-      </c>
-      <c r="G20" s="60">
-        <v>41.558183374930195</v>
+        <v>175</v>
+      </c>
+      <c r="C20" s="55">
+        <v>0.5367057761732852</v>
+      </c>
+      <c r="D20" s="55">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E20" s="55">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F20" s="55">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G20" s="55">
+        <v>0.3112549289361249</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="61">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D21" s="55">
+        <v>0.10882435861291231</v>
+      </c>
+      <c r="E21" s="55">
+        <v>0.08912573081650489</v>
+      </c>
+      <c r="F21" s="55">
+        <v>0.07842836821053388</v>
+      </c>
+      <c r="G21" s="55">
+        <v>0.07828025286532257</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="55">
+        <v>0.24398014440433213</v>
+      </c>
+      <c r="D22" s="55">
+        <v>0.4068755286157316</v>
+      </c>
+      <c r="E22" s="55">
+        <v>0.5061082473022297</v>
+      </c>
+      <c r="F22" s="55">
+        <v>0.5598699747062044</v>
+      </c>
+      <c r="G22" s="55">
+        <v>0.5604445004214422</v>
+      </c>
+      <c r="H22" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="62">
+        <v>3</v>
+      </c>
+      <c r="D23" s="62">
+        <v>3</v>
+      </c>
+      <c r="E23" s="62">
+        <v>3</v>
+      </c>
+      <c r="F23" s="62">
+        <v>3</v>
+      </c>
+      <c r="G23" s="62">
+        <v>3</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" s="63">
+        <v>7.768317132140687</v>
+      </c>
+      <c r="D24" s="63">
+        <v>19.906582055072757</v>
+      </c>
+      <c r="E24" s="63">
+        <v>31.11967785112557</v>
+      </c>
+      <c r="F24" s="63">
+        <v>40.26332017079355</v>
+      </c>
+      <c r="G24" s="63">
+        <v>41.558183374930195</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="61" t="str">
+      <c r="D25" s="64" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="61" t="str">
+      <c r="E25" s="64" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="61" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="61" t="str">
+      <c r="G25" s="64" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H25" s="57" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="62">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="65">
         <v>3</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D26" s="65">
         <v>10</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E26" s="66">
         <v>21</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F26" s="62">
         <v>35</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G26" s="62">
         <v>48</v>
       </c>
-      <c r="H22" s="57" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="53" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="59">
+      <c r="H26" s="57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="62">
         <v>99</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D27" s="62">
         <v>312</v>
       </c>
-      <c r="E23" s="59">
+      <c r="E27" s="62">
         <v>649</v>
       </c>
-      <c r="F23" s="59">
+      <c r="F27" s="62">
         <v>1063</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G27" s="62">
         <v>1473</v>
       </c>
-      <c r="H23" s="57" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
+      <c r="H27" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="40" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="C29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66" t="s">
+      <c r="D29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="65" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66" t="s">
+      <c r="C30" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="64" t="s">
+      <c r="D30" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="65" t="s">
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66" t="s">
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
+      <c r="C31" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="65" t="s">
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
         <v>200</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66" t="s">
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
+      <c r="C32" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="65" t="s">
+      <c r="E32" s="68"/>
+      <c r="F32" s="69" t="s">
         <v>203</v>
       </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66" t="s">
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
+      <c r="C33" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="65" t="s">
+      <c r="E33" s="68"/>
+      <c r="F33" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66" t="s">
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
+      <c r="C34" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D32" s="65" t="s">
+      <c r="E34" s="68"/>
+      <c r="F34" s="69" t="s">
         <v>209</v>
       </c>
-      <c r="E32" s="65"/>
-      <c r="F32" s="66" t="s">
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="64" t="s">
+      <c r="C35" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="68"/>
+      <c r="F36" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="53" t="s">
-        <v>211</v>
-      </c>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="67" t="s">
-        <v>212</v>
-      </c>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
+      <c r="C38" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="70" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -4587,8 +4686,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4634,48 +4741,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="211">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -549,21 +549,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -601,12 +586,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -946,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,15 +1002,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3995,7 +3965,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4244,458 +4214,352 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="58">
-        <v>14541.150712549514</v>
-      </c>
-      <c r="D16" s="58">
-        <v>11606.989363921899</v>
-      </c>
-      <c r="E16" s="58">
-        <v>9923.582206845189</v>
-      </c>
-      <c r="F16" s="58">
-        <v>9090.112342023767</v>
-      </c>
-      <c r="G16" s="58">
-        <v>9352.312342023766</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="C16" s="55">
+        <v>0.5367057761732852</v>
+      </c>
+      <c r="D16" s="55">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F16" s="55">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G16" s="55">
+        <v>0.3112549289361249</v>
+      </c>
+      <c r="H16" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="52">
-        <v>500</v>
-      </c>
-      <c r="D17" s="52">
-        <v>515</v>
-      </c>
-      <c r="E17" s="52">
-        <v>530</v>
-      </c>
-      <c r="F17" s="52">
-        <v>546</v>
-      </c>
-      <c r="G17" s="52">
-        <v>562</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="58">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D17" s="55">
+        <v>0.10882435861291231</v>
+      </c>
+      <c r="E17" s="55">
+        <v>0.08912573081650489</v>
+      </c>
+      <c r="F17" s="55">
+        <v>0.07842836821053388</v>
+      </c>
+      <c r="G17" s="55">
+        <v>0.07828025286532257</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="59">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="59">
-        <v>2058.6666666666665</v>
-      </c>
-      <c r="E18" s="56">
-        <v>1733.6818181818182</v>
-      </c>
-      <c r="F18" s="56">
-        <v>1570.1924</v>
-      </c>
-      <c r="G18" s="56">
-        <v>1615.9705720000002</v>
+      <c r="B18" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="55">
+        <v>0.24398014440433213</v>
+      </c>
+      <c r="D18" s="55">
+        <v>0.4068755286157316</v>
+      </c>
+      <c r="E18" s="55">
+        <v>0.5061082473022297</v>
+      </c>
+      <c r="F18" s="55">
+        <v>0.5598699747062044</v>
+      </c>
+      <c r="G18" s="55">
+        <v>0.5604445004214422</v>
       </c>
       <c r="H18" s="57" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="60">
-        <v>3925.5</v>
-      </c>
-      <c r="D19" s="60">
-        <v>7310.333333333333</v>
-      </c>
-      <c r="E19" s="60">
-        <v>9528.5</v>
-      </c>
-      <c r="F19" s="60">
-        <v>10930.6</v>
-      </c>
-      <c r="G19" s="60">
-        <v>11291.08</v>
+        <v>176</v>
+      </c>
+      <c r="C19" s="59">
+        <v>3</v>
+      </c>
+      <c r="D19" s="59">
+        <v>3</v>
+      </c>
+      <c r="E19" s="59">
+        <v>3</v>
+      </c>
+      <c r="F19" s="59">
+        <v>3</v>
+      </c>
+      <c r="G19" s="59">
+        <v>3</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="C20" s="55">
-        <v>0.5367057761732852</v>
-      </c>
-      <c r="D20" s="55">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E20" s="55">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F20" s="55">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G20" s="55">
-        <v>0.3112549289361249</v>
+        <v>178</v>
+      </c>
+      <c r="C20" s="60">
+        <v>7.768317132140687</v>
+      </c>
+      <c r="D20" s="60">
+        <v>19.906582055072757</v>
+      </c>
+      <c r="E20" s="60">
+        <v>31.11967785112557</v>
+      </c>
+      <c r="F20" s="60">
+        <v>40.26332017079355</v>
+      </c>
+      <c r="G20" s="60">
+        <v>41.558183374930195</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="61">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D21" s="55">
-        <v>0.10882435861291231</v>
-      </c>
-      <c r="E21" s="55">
-        <v>0.08912573081650489</v>
-      </c>
-      <c r="F21" s="55">
-        <v>0.07842836821053388</v>
-      </c>
-      <c r="G21" s="55">
-        <v>0.07828025286532257</v>
+        <v>180</v>
+      </c>
+      <c r="C21" s="40" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="61" t="str">
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="61" t="str">
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="61" t="str">
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="61" t="str">
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="57" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="55">
-        <v>0.24398014440433213</v>
-      </c>
-      <c r="D22" s="55">
-        <v>0.4068755286157316</v>
-      </c>
-      <c r="E22" s="55">
-        <v>0.5061082473022297</v>
-      </c>
-      <c r="F22" s="55">
-        <v>0.5598699747062044</v>
-      </c>
-      <c r="G22" s="55">
-        <v>0.5604445004214422</v>
+        <v>181</v>
+      </c>
+      <c r="C22" s="62">
+        <v>3</v>
+      </c>
+      <c r="D22" s="62">
+        <v>10</v>
+      </c>
+      <c r="E22" s="63">
+        <v>21</v>
+      </c>
+      <c r="F22" s="59">
+        <v>35</v>
+      </c>
+      <c r="G22" s="59">
+        <v>48</v>
       </c>
       <c r="H22" s="57" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="62">
-        <v>3</v>
-      </c>
-      <c r="D23" s="62">
-        <v>3</v>
-      </c>
-      <c r="E23" s="62">
-        <v>3</v>
-      </c>
-      <c r="F23" s="62">
-        <v>3</v>
-      </c>
-      <c r="G23" s="62">
-        <v>3</v>
-      </c>
-      <c r="H23" s="57" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="53" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="63">
-        <v>7.768317132140687</v>
-      </c>
-      <c r="D24" s="63">
-        <v>19.906582055072757</v>
-      </c>
-      <c r="E24" s="63">
-        <v>31.11967785112557</v>
-      </c>
-      <c r="F24" s="63">
-        <v>40.26332017079355</v>
-      </c>
-      <c r="G24" s="63">
-        <v>41.558183374930195</v>
-      </c>
-      <c r="H24" s="57" t="s">
+      <c r="C24" s="8" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="53" t="s">
+      <c r="D24" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="64" t="str">
-        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="64" t="str">
-        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="64" t="str">
-        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="64" t="str">
-        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="53" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C26" s="65">
-        <v>3</v>
-      </c>
-      <c r="D26" s="65">
-        <v>10</v>
-      </c>
-      <c r="E26" s="66">
-        <v>21</v>
-      </c>
-      <c r="F26" s="62">
-        <v>35</v>
-      </c>
-      <c r="G26" s="62">
-        <v>48</v>
-      </c>
-      <c r="H26" s="57" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="64" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="C25" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="62">
-        <v>99</v>
-      </c>
-      <c r="D27" s="62">
-        <v>312</v>
-      </c>
-      <c r="E27" s="62">
-        <v>649</v>
-      </c>
-      <c r="F27" s="62">
-        <v>1063</v>
-      </c>
-      <c r="G27" s="62">
-        <v>1473</v>
-      </c>
-      <c r="H27" s="57" t="s">
+      <c r="D25" s="65" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="E25" s="65"/>
+      <c r="F25" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C26" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="E26" s="65"/>
+      <c r="F26" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="64" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="65"/>
+      <c r="F29" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="67" t="s">
-        <v>194</v>
+      <c r="B30" s="64" t="s">
+        <v>203</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+        <v>188</v>
+      </c>
+      <c r="D30" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66" t="s">
+        <v>205</v>
+      </c>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="67" t="s">
-        <v>198</v>
+      <c r="B31" s="64" t="s">
+        <v>206</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
-        <v>200</v>
-      </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>202</v>
-      </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="67" t="s">
-        <v>204</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>205</v>
-      </c>
-      <c r="E33" s="68"/>
-      <c r="F33" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="68" t="s">
+      <c r="E31" s="65"/>
+      <c r="F31" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69" t="s">
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="67" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>214</v>
-      </c>
-      <c r="E36" s="68"/>
-      <c r="F36" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4741,48 +4605,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="218">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -549,6 +549,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -586,6 +601,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -925,7 +946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1002,6 +1023,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3965,7 +3995,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4214,352 +4244,458 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="55">
-        <v>0.5367057761732852</v>
-      </c>
-      <c r="D16" s="55">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E16" s="55">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F16" s="55">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G16" s="55">
-        <v>0.3112549289361249</v>
-      </c>
-      <c r="H16" s="57" t="s">
+      <c r="C16" s="58">
+        <v>14541.150712549514</v>
+      </c>
+      <c r="D16" s="58">
+        <v>11606.989363921899</v>
+      </c>
+      <c r="E16" s="58">
+        <v>9923.582206845189</v>
+      </c>
+      <c r="F16" s="58">
+        <v>9090.112342023767</v>
+      </c>
+      <c r="G16" s="58">
+        <v>9352.312342023766</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="53" t="s">
+      <c r="C17" s="52">
+        <v>500</v>
+      </c>
+      <c r="D17" s="52">
+        <v>515</v>
+      </c>
+      <c r="E17" s="52">
+        <v>530</v>
+      </c>
+      <c r="F17" s="52">
+        <v>546</v>
+      </c>
+      <c r="G17" s="52">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="58">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D17" s="55">
-        <v>0.10882435861291231</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0.08912573081650489</v>
-      </c>
-      <c r="F17" s="55">
-        <v>0.07842836821053388</v>
-      </c>
-      <c r="G17" s="55">
-        <v>0.07828025286532257</v>
-      </c>
-      <c r="H17" s="57" t="s">
+      <c r="C18" s="59">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="59">
+        <v>2058.6666666666665</v>
+      </c>
+      <c r="E18" s="56">
+        <v>1733.6818181818182</v>
+      </c>
+      <c r="F18" s="56">
+        <v>1570.1924</v>
+      </c>
+      <c r="G18" s="56">
+        <v>1615.9705720000002</v>
+      </c>
+      <c r="H18" s="57" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="53" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="C18" s="55">
-        <v>0.24398014440433213</v>
-      </c>
-      <c r="D18" s="55">
-        <v>0.4068755286157316</v>
-      </c>
-      <c r="E18" s="55">
-        <v>0.5061082473022297</v>
-      </c>
-      <c r="F18" s="55">
-        <v>0.5598699747062044</v>
-      </c>
-      <c r="G18" s="55">
-        <v>0.5604445004214422</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="59">
-        <v>3</v>
-      </c>
-      <c r="D19" s="59">
-        <v>3</v>
-      </c>
-      <c r="E19" s="59">
-        <v>3</v>
-      </c>
-      <c r="F19" s="59">
-        <v>3</v>
-      </c>
-      <c r="G19" s="59">
-        <v>3</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>177</v>
+      <c r="C19" s="60">
+        <v>3925.5</v>
+      </c>
+      <c r="D19" s="60">
+        <v>7310.333333333333</v>
+      </c>
+      <c r="E19" s="60">
+        <v>9528.5</v>
+      </c>
+      <c r="F19" s="60">
+        <v>10930.6</v>
+      </c>
+      <c r="G19" s="60">
+        <v>11291.08</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="60">
-        <v>7.768317132140687</v>
-      </c>
-      <c r="D20" s="60">
-        <v>19.906582055072757</v>
-      </c>
-      <c r="E20" s="60">
-        <v>31.11967785112557</v>
-      </c>
-      <c r="F20" s="60">
-        <v>40.26332017079355</v>
-      </c>
-      <c r="G20" s="60">
-        <v>41.558183374930195</v>
+        <v>175</v>
+      </c>
+      <c r="C20" s="55">
+        <v>0.5367057761732852</v>
+      </c>
+      <c r="D20" s="55">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E20" s="55">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F20" s="55">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G20" s="55">
+        <v>0.3112549289361249</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="61">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D21" s="55">
+        <v>0.10882435861291231</v>
+      </c>
+      <c r="E21" s="55">
+        <v>0.08912573081650489</v>
+      </c>
+      <c r="F21" s="55">
+        <v>0.07842836821053388</v>
+      </c>
+      <c r="G21" s="55">
+        <v>0.07828025286532257</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="55">
+        <v>0.24398014440433213</v>
+      </c>
+      <c r="D22" s="55">
+        <v>0.4068755286157316</v>
+      </c>
+      <c r="E22" s="55">
+        <v>0.5061082473022297</v>
+      </c>
+      <c r="F22" s="55">
+        <v>0.5598699747062044</v>
+      </c>
+      <c r="G22" s="55">
+        <v>0.5604445004214422</v>
+      </c>
+      <c r="H22" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="62">
+        <v>3</v>
+      </c>
+      <c r="D23" s="62">
+        <v>3</v>
+      </c>
+      <c r="E23" s="62">
+        <v>3</v>
+      </c>
+      <c r="F23" s="62">
+        <v>3</v>
+      </c>
+      <c r="G23" s="62">
+        <v>3</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" s="63">
+        <v>7.768317132140687</v>
+      </c>
+      <c r="D24" s="63">
+        <v>19.906582055072757</v>
+      </c>
+      <c r="E24" s="63">
+        <v>31.11967785112557</v>
+      </c>
+      <c r="F24" s="63">
+        <v>40.26332017079355</v>
+      </c>
+      <c r="G24" s="63">
+        <v>41.558183374930195</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="61" t="str">
+      <c r="D25" s="64" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="61" t="str">
+      <c r="E25" s="64" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="61" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="61" t="str">
+      <c r="G25" s="64" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H25" s="57" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="62">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="65">
         <v>3</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D26" s="65">
         <v>10</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E26" s="66">
         <v>21</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F26" s="62">
         <v>35</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G26" s="62">
         <v>48</v>
       </c>
-      <c r="H22" s="57" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="H26" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="40" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="65" t="s">
+      <c r="C27" s="62">
+        <v>99</v>
+      </c>
+      <c r="D27" s="62">
+        <v>312</v>
+      </c>
+      <c r="E27" s="62">
+        <v>649</v>
+      </c>
+      <c r="F27" s="62">
+        <v>1063</v>
+      </c>
+      <c r="G27" s="62">
+        <v>1473</v>
+      </c>
+      <c r="H27" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
+      <c r="C29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="65" t="s">
+      <c r="D29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="65" t="s">
+      <c r="C30" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66" t="s">
+      <c r="D30" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="64" t="s">
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="65" t="s">
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66" t="s">
+      <c r="C31" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="65" t="s">
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66" t="s">
+      <c r="C32" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
+      <c r="E32" s="68"/>
+      <c r="F32" s="69" t="s">
         <v>203</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="65" t="s">
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66" t="s">
+      <c r="C33" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
+      <c r="E33" s="68"/>
+      <c r="F33" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="65" t="s">
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66" t="s">
+      <c r="C34" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="53" t="s">
+      <c r="E34" s="68"/>
+      <c r="F34" s="69" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
+      <c r="C35" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="68"/>
+      <c r="F36" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="70" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4605,48 +4741,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -15,7 +15,7 @@
     <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="219">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -168,6 +168,9 @@
     <t>July</t>
   </si>
   <si>
+    <t>Accounting Basis</t>
+  </si>
+  <si>
     <t>Year 1 Operating Months</t>
   </si>
   <si>
@@ -507,7 +510,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1571,7 +1574,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1688,70 +1691,70 @@
       <c r="A14" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="23">
-        <v>10</v>
+      <c r="B14" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>45</v>
+      <c r="B15" s="23">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="24">
-        <v>12</v>
-      </c>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="24">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1759,7 +1762,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="24">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1767,7 +1770,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="24">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1778,42 +1781,50 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="B27" s="24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="25">
-        <v>0.03</v>
-      </c>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>62</v>
       </c>
       <c r="B30" s="25">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="26">
-        <v>0.8333333333333334</v>
+      <c r="B31" s="25">
+        <v>0.025</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>65</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1846,49 +1857,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>12</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>18</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>22</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
-        <v>25</v>
-      </c>
-      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
+      <c r="F2" s="29">
+        <f>Assumptions!B27</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1898,57 +1909,57 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="30">
-        <f>12000*Assumptions!B22</f>
+        <f>12000*Assumptions!B23</f>
         <v>144000</v>
       </c>
       <c r="C4" s="30">
-        <f>12360*Assumptions!B23</f>
+        <f>12360*Assumptions!B24</f>
         <v>222480</v>
       </c>
       <c r="D4" s="30">
-        <f>12731*Assumptions!B24</f>
+        <f>12731*Assumptions!B25</f>
         <v>280082</v>
       </c>
       <c r="E4" s="30">
-        <f>13113*Assumptions!B25</f>
+        <f>13113*Assumptions!B26</f>
         <v>327825</v>
       </c>
       <c r="F4" s="30">
-        <f>13506*Assumptions!B26</f>
+        <f>13506*Assumptions!B27</f>
         <v>337650</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="30">
-        <f>250*Assumptions!B22</f>
+        <f>250*Assumptions!B23</f>
         <v>3000</v>
       </c>
       <c r="C5" s="30">
-        <f>250*Assumptions!B23</f>
+        <f>250*Assumptions!B24</f>
         <v>4500</v>
       </c>
       <c r="D5" s="30">
-        <f>250*Assumptions!B24</f>
+        <f>250*Assumptions!B25</f>
         <v>5500</v>
       </c>
       <c r="E5" s="30">
-        <f>250*Assumptions!B25</f>
-        <v>6250</v>
-      </c>
-      <c r="F5" s="30">
         <f>250*Assumptions!B26</f>
         <v>6250</v>
       </c>
+      <c r="F5" s="30">
+        <f>250*Assumptions!B27</f>
+        <v>6250</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B4:B5)</f>
@@ -1973,7 +1984,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1983,7 +1994,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="30">
         <f>-B4*0.1</f>
@@ -2008,7 +2019,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -2033,7 +2044,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2043,32 +2054,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="30">
-        <f>7000*Assumptions!B22</f>
+        <f>7000*Assumptions!B23</f>
         <v>84000</v>
       </c>
       <c r="C11" s="30">
-        <f>7210*Assumptions!B23</f>
+        <f>7210*Assumptions!B24</f>
         <v>129780</v>
       </c>
       <c r="D11" s="30">
-        <f>7426*Assumptions!B24</f>
+        <f>7426*Assumptions!B25</f>
         <v>163372</v>
       </c>
       <c r="E11" s="30">
-        <f>7649*Assumptions!B25</f>
+        <f>7649*Assumptions!B26</f>
         <v>191225</v>
       </c>
       <c r="F11" s="30">
-        <f>7878*Assumptions!B26</f>
+        <f>7878*Assumptions!B27</f>
         <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B11:B11)</f>
@@ -2093,7 +2104,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2103,7 +2114,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="30">
         <v>5000</v>
@@ -2123,7 +2134,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
@@ -2148,7 +2159,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31">
         <f>B6+B9+B12+B15</f>
@@ -2195,7 +2206,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2207,39 +2218,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" s="26">
         <v>1</v>
@@ -2259,13 +2270,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>98</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>97</v>
       </c>
       <c r="D5" s="26">
         <v>1</v>
@@ -2285,13 +2296,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="C6" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="26">
         <v>0.5</v>
@@ -2311,7 +2322,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2323,7 +2334,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="34">
         <v>3</v>
@@ -2331,7 +2342,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" s="34">
         <v>2.5</v>
@@ -2339,7 +2350,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="35">
         <v>114000</v>
@@ -2347,7 +2358,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="35">
         <v>20000</v>
@@ -2355,7 +2366,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="35">
         <v>8721</v>
@@ -2363,7 +2374,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="35">
         <v>0</v>
@@ -2371,7 +2382,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="36">
         <v>142721</v>
@@ -2379,7 +2390,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2392,24 +2403,24 @@
         <v>23</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="30">
         <v>142721</v>
@@ -2429,35 +2440,35 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="37">
-        <f>(1+Assumptions!B29)^0</f>
+        <f>(1+Assumptions!B30)^0</f>
         <v>1</v>
       </c>
       <c r="C20" s="37">
-        <f>(1+Assumptions!B29)^1</f>
+        <f>(1+Assumptions!B30)^1</f>
         <v>1.03</v>
       </c>
       <c r="D20" s="37">
-        <f>(1+Assumptions!B29)^2</f>
+        <f>(1+Assumptions!B30)^2</f>
         <v>1.0609</v>
       </c>
       <c r="E20" s="37">
-        <f>(1+Assumptions!B29)^3</f>
+        <f>(1+Assumptions!B30)^3</f>
         <v>1.092727</v>
       </c>
       <c r="F20" s="37">
-        <f>(1+Assumptions!B29)^4</f>
+        <f>(1+Assumptions!B30)^4</f>
         <v>1.1255088100000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="38">
-        <f>Assumptions!B31</f>
+        <f>Assumptions!B32</f>
         <v>0.8333333333333334</v>
       </c>
       <c r="C21" s="38">
@@ -2475,7 +2486,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" s="31">
         <f>B19*B20*B21</f>
@@ -2528,49 +2539,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>12</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>18</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>22</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
-        <v>25</v>
-      </c>
-      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>25</v>
       </c>
+      <c r="F2" s="29">
+        <f>Assumptions!B27</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2580,32 +2591,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="30">
-        <f>500*Assumptions!B22</f>
+        <f>500*Assumptions!B23</f>
         <v>6000</v>
       </c>
       <c r="C4" s="30">
-        <f>515*Assumptions!B23</f>
+        <f>515*Assumptions!B24</f>
         <v>9270</v>
       </c>
       <c r="D4" s="30">
-        <f>530*Assumptions!B24</f>
+        <f>530*Assumptions!B25</f>
         <v>11660</v>
       </c>
       <c r="E4" s="30">
-        <f>546*Assumptions!B25</f>
+        <f>546*Assumptions!B26</f>
         <v>13650</v>
       </c>
       <c r="F4" s="30">
-        <f>562*Assumptions!B26</f>
+        <f>562*Assumptions!B27</f>
         <v>14050</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -2630,7 +2641,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2640,32 +2651,32 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="30">
-        <f>300*Assumptions!B22</f>
+        <f>300*Assumptions!B23</f>
         <v>3600</v>
       </c>
       <c r="C7" s="30">
-        <f>309*Assumptions!B23</f>
+        <f>309*Assumptions!B24</f>
         <v>5562</v>
       </c>
       <c r="D7" s="30">
-        <f>318*Assumptions!B24</f>
+        <f>318*Assumptions!B25</f>
         <v>6996</v>
       </c>
       <c r="E7" s="30">
-        <f>328*Assumptions!B25</f>
+        <f>328*Assumptions!B26</f>
         <v>8200</v>
       </c>
       <c r="F7" s="30">
-        <f>338*Assumptions!B26</f>
+        <f>338*Assumptions!B27</f>
         <v>8450</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -2690,7 +2701,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2700,7 +2711,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B10" s="30">
         <f>2500*12</f>
@@ -2725,7 +2736,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="30">
         <f>300*12</f>
@@ -2750,7 +2761,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" s="30">
         <v>2400</v>
@@ -2770,7 +2781,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -2795,7 +2806,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2805,7 +2816,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" s="30">
         <v>3000</v>
@@ -2825,7 +2836,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
@@ -2850,7 +2861,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="31">
         <f>B5+B8+B13+B16</f>
@@ -2900,24 +2911,24 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2927,7 +2938,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="30">
         <v>6959.808550594178</v>
@@ -2947,7 +2958,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="31">
         <f>SUM(B3:B3)</f>
@@ -2997,24 +3008,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B17</f>
@@ -3039,7 +3050,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B22</f>
@@ -3114,7 +3125,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -3139,7 +3150,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -3164,7 +3175,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -3214,10 +3225,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>23</v>
@@ -3247,7 +3258,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3256,7 +3267,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -3266,7 +3277,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3337,134 +3348,117 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B16" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="C16" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="E16" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="F16" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="29">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>12</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>18</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D17" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>22</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E17" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>25</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F17" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="44">
-        <f>IF(B16=0,0,(C16-B16)/B16)</f>
+      <c r="B18" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="44">
+        <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="44">
-        <f>IF(C16=0,0,(D16-C16)/C16)</f>
+      <c r="D18" s="44">
+        <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E17" s="44">
-        <f>IF(D16=0,0,(E16-D16)/D16)</f>
+      <c r="E18" s="44">
+        <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F17" s="44" t="str">
-        <f>IF(E16=0,0,(F16-E16)/E16)</f>
+      <c r="F18" s="44" t="str">
+        <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="B20" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="C20" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="30">
-        <f>'Financial Model'!B2</f>
-        <v>221600</v>
-      </c>
-      <c r="C20" s="30">
-        <f>'Financial Model'!C2</f>
-        <v>340512</v>
-      </c>
-      <c r="D20" s="30">
-        <f>'Financial Model'!D2</f>
-        <v>427946</v>
-      </c>
-      <c r="E20" s="30">
-        <f>'Financial Model'!E2</f>
-        <v>500518</v>
-      </c>
-      <c r="F20" s="30">
-        <f>'Financial Model'!F2</f>
-        <v>516085</v>
+      <c r="F20" s="28" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3472,209 +3466,209 @@
         <v>134</v>
       </c>
       <c r="B21" s="30">
+        <f>'Financial Model'!B2</f>
+        <v>221600</v>
+      </c>
+      <c r="C21" s="30">
+        <f>'Financial Model'!C2</f>
+        <v>340512</v>
+      </c>
+      <c r="D21" s="30">
+        <f>'Financial Model'!D2</f>
+        <v>427946</v>
+      </c>
+      <c r="E21" s="30">
+        <f>'Financial Model'!E2</f>
+        <v>500518</v>
+      </c>
+      <c r="F21" s="30">
+        <f>'Financial Model'!F2</f>
+        <v>516085</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
         <v>118934</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f>'Financial Model'!C3</f>
         <v>147003</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D22" s="30">
         <f>'Financial Model'!D3</f>
         <v>151413</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E22" s="30">
         <f>'Financial Model'!E3</f>
         <v>155955</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F22" s="30">
         <f>'Financial Model'!F3</f>
         <v>160634</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B23" s="30">
         <f>'Financial Model'!B4</f>
         <v>48600</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f>'Financial Model'!C4</f>
         <v>54963</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="30">
         <f>'Financial Model'!D4</f>
         <v>59946</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E23" s="30">
         <f>'Financial Model'!E4</f>
         <v>64338</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F23" s="30">
         <f>'Financial Model'!F4</f>
         <v>66214</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="31">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
         <v>174494</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f>'Financial Model'!C6</f>
         <v>208926</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D24" s="31">
         <f>'Financial Model'!D6</f>
         <v>218319</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="31">
         <f>'Financial Model'!E6</f>
         <v>227253</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F24" s="31">
         <f>'Financial Model'!F6</f>
         <v>233808</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="45">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C24" s="45">
+      <c r="C25" s="45">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D24" s="45">
+      <c r="D25" s="45">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E25" s="45">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F24" s="45">
+      <c r="F25" s="45">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="30">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f>'Financial Model'!C8</f>
         <v>178692</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D26" s="30">
         <f>'Financial Model'!D8</f>
         <v>388319</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E26" s="30">
         <f>'Financial Model'!E8</f>
         <v>661584</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F26" s="30">
         <f>'Financial Model'!F8</f>
         <v>943861</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B27" s="13">
         <f>'Financial Model'!B9</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C27" s="13">
         <f>'Financial Model'!C9</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D27" s="13">
         <f>'Financial Model'!D9</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="13">
         <f>'Financial Model'!E9</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F27" s="13">
         <f>'Financial Model'!F9</f>
         <v>48.44287620611784</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B29" s="30">
-        <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>18466.666666666668</v>
-      </c>
-      <c r="C29" s="30">
-        <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>18917.333333333332</v>
-      </c>
-      <c r="D29" s="30">
-        <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>19452.090909090908</v>
-      </c>
-      <c r="E29" s="30">
-        <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>20020.72</v>
-      </c>
-      <c r="F29" s="30">
-        <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>20643.4</v>
-      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.5367057761732852</v>
-      </c>
-      <c r="C30" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="D30" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="E30" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="F30" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.3112549289361249</v>
+      <c r="B30" s="30">
+        <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
+        <v>18466.666666666668</v>
+      </c>
+      <c r="C30" s="30">
+        <f>IF('Revenue Schedule'!C2=0,0,C21/'Revenue Schedule'!C2)</f>
+        <v>18917.333333333332</v>
+      </c>
+      <c r="D30" s="30">
+        <f>IF('Revenue Schedule'!D2=0,0,D21/'Revenue Schedule'!D2)</f>
+        <v>19452.090909090908</v>
+      </c>
+      <c r="E30" s="30">
+        <f>IF('Revenue Schedule'!E2=0,0,E21/'Revenue Schedule'!E2)</f>
+        <v>20020.72</v>
+      </c>
+      <c r="F30" s="30">
+        <f>IF('Revenue Schedule'!F2=0,0,F21/'Revenue Schedule'!F2)</f>
+        <v>20643.4</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3682,99 +3676,104 @@
         <v>149</v>
       </c>
       <c r="B31" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
+        <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
+        <v>0.5367057761732852</v>
+      </c>
+      <c r="C31" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="D31" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="E31" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="F31" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
+        <v>0.3112549289361249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="44">
+        <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C31" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
+      <c r="C32" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D31" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
+      <c r="D32" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E31" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
+      <c r="E32" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F31" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
+      <c r="F32" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B32" s="12">
-        <f>IF(B20=0,0,B24/B20)</f>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="12">
+        <f>IF(B21=0,0,B25/B21)</f>
         <v>0.21257220216606498</v>
       </c>
-      <c r="C32" s="12">
-        <f>IF(C20=0,0,C24/C20)</f>
+      <c r="C33" s="12">
+        <f>IF(C21=0,0,C25/C21)</f>
         <v>0.38643572032703694</v>
       </c>
-      <c r="D32" s="12">
-        <f>IF(D20=0,0,D24/D20)</f>
+      <c r="D33" s="12">
+        <f>IF(D21=0,0,D25/D21)</f>
         <v>0.4898445130927734</v>
       </c>
-      <c r="E32" s="12">
-        <f>IF(E20=0,0,E24/E20)</f>
+      <c r="E33" s="12">
+        <f>IF(E21=0,0,E25/E21)</f>
         <v>0.5459643809013862</v>
       </c>
-      <c r="F32" s="12">
-        <f>IF(F20=0,0,F24/F20)</f>
+      <c r="F33" s="12">
+        <f>IF(F21=0,0,F25/F21)</f>
         <v>0.5469583498842245</v>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B35" s="44">
-        <v>0.5983754512635379</v>
-      </c>
-      <c r="C35" s="44">
-        <v>0.6012475331265859</v>
-      </c>
-      <c r="D35" s="44">
-        <v>0.6018841638357006</v>
-      </c>
-      <c r="E35" s="44">
-        <v>0.6019619693617106</v>
-      </c>
-      <c r="F35" s="44">
-        <v>0.6009378300086227</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>153</v>
       </c>
       <c r="B36" s="44">
-        <v>0.37906137184115524</v>
+        <v>0.5983754512635379</v>
       </c>
       <c r="C36" s="44">
-        <v>0.3811319424866084</v>
+        <v>0.6012475331265859</v>
       </c>
       <c r="D36" s="44">
-        <v>0.3817586245734857</v>
+        <v>0.6018841638357006</v>
       </c>
       <c r="E36" s="44">
-        <v>0.38205457351641053</v>
+        <v>0.6019619693617106</v>
       </c>
       <c r="F36" s="44">
-        <v>0.3816231822277338</v>
+        <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3782,18 +3781,38 @@
         <v>154</v>
       </c>
       <c r="B37" s="44">
+        <v>0.37906137184115524</v>
+      </c>
+      <c r="C37" s="44">
+        <v>0.3811319424866084</v>
+      </c>
+      <c r="D37" s="44">
+        <v>0.3817586245734857</v>
+      </c>
+      <c r="E37" s="44">
+        <v>0.38205457351641053</v>
+      </c>
+      <c r="F37" s="44">
+        <v>0.3816231822277338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="44">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C38" s="44">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D38" s="44">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E38" s="44">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F38" s="44">
         <v>0.017438987763643585</v>
       </c>
     </row>
@@ -4007,7 +4026,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -4018,7 +4037,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" s="46"/>
       <c r="D3" s="46"/>
@@ -4029,41 +4048,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4" s="49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" s="51">
         <v>12</v>
@@ -4083,7 +4102,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="52">
         <v>221600</v>
@@ -4103,7 +4122,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C9" s="52">
         <v>118934</v>
@@ -4143,7 +4162,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C11" s="52">
         <v>6959.808550594178</v>
@@ -4163,7 +4182,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="53" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C12" s="54">
         <v>47106</v>
@@ -4183,7 +4202,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="54">
         <v>47106</v>
@@ -4203,7 +4222,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="55">
         <v>0.21257220216606498</v>
@@ -4223,7 +4242,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="56">
         <v>18466.666666666668</v>
@@ -4241,12 +4260,12 @@
         <v>20643.4</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="58">
         <v>14541.150712549514</v>
@@ -4266,7 +4285,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="52">
         <v>500</v>
@@ -4286,7 +4305,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C18" s="59">
         <v>3000</v>
@@ -4304,12 +4323,12 @@
         <v>1615.9705720000002</v>
       </c>
       <c r="H18" s="57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C19" s="60">
         <v>3925.5</v>
@@ -4329,7 +4348,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C20" s="55">
         <v>0.5367057761732852</v>
@@ -4347,12 +4366,12 @@
         <v>0.3112549289361249</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="61">
         <v>0.1624548736462094</v>
@@ -4370,12 +4389,12 @@
         <v>0.07828025286532257</v>
       </c>
       <c r="H21" s="57" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C22" s="55">
         <v>0.24398014440433213</v>
@@ -4393,12 +4412,12 @@
         <v>0.5604445004214422</v>
       </c>
       <c r="H22" s="57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" s="62">
         <v>3</v>
@@ -4416,12 +4435,12 @@
         <v>3</v>
       </c>
       <c r="H23" s="57" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C24" s="63">
         <v>7.768317132140687</v>
@@ -4439,12 +4458,12 @@
         <v>41.558183374930195</v>
       </c>
       <c r="H24" s="57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
@@ -4467,12 +4486,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" s="65">
         <v>3</v>
@@ -4490,12 +4509,12 @@
         <v>48</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C27" s="62">
         <v>99</v>
@@ -4513,141 +4532,141 @@
         <v>1473</v>
       </c>
       <c r="H27" s="57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="67" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E30" s="68"/>
       <c r="F30" s="69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="69"/>
       <c r="H30" s="69"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E31" s="68"/>
       <c r="F31" s="69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G31" s="69"/>
       <c r="H31" s="69"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D32" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E32" s="68"/>
       <c r="F32" s="69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G32" s="69"/>
       <c r="H32" s="69"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D33" s="68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E33" s="68"/>
       <c r="F33" s="69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G33" s="69"/>
       <c r="H33" s="69"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D34" s="68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E34" s="68"/>
       <c r="F34" s="69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G34" s="69"/>
       <c r="H34" s="69"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D35" s="68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E35" s="68"/>
       <c r="F35" s="69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G35" s="69"/>
       <c r="H35" s="69"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E36" s="68"/>
       <c r="F36" s="69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G36" s="69"/>
       <c r="H36" s="69"/>
@@ -4657,7 +4676,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D38" s="53"/>
       <c r="E38" s="53"/>
@@ -4665,7 +4684,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="70" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C40" s="70"/>
       <c r="D40" s="70"/>
@@ -4779,10 +4798,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -522,7 +522,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -522,7 +522,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -645,7 +645,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1870,7 +1870,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1880,7 +1880,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>159</v>
       </c>
@@ -1890,8 +1890,9 @@
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="48" t="s">
         <v>160</v>
       </c>
@@ -1901,6 +1902,7 @@
       <c r="F3" s="48"/>
       <c r="G3" s="48"/>
       <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="49" t="s">
@@ -2391,7 +2393,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>194</v>
       </c>
@@ -2407,8 +2409,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="69" t="s">
         <v>198</v>
       </c>
@@ -2424,8 +2427,9 @@
       </c>
       <c r="G30" s="71"/>
       <c r="H30" s="71"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="71"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="69" t="s">
         <v>202</v>
       </c>
@@ -2441,8 +2445,9 @@
       </c>
       <c r="G31" s="71"/>
       <c r="H31" s="71"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="71"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="69" t="s">
         <v>205</v>
       </c>
@@ -2458,8 +2463,9 @@
       </c>
       <c r="G32" s="71"/>
       <c r="H32" s="71"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="71"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="69" t="s">
         <v>208</v>
       </c>
@@ -2475,8 +2481,9 @@
       </c>
       <c r="G33" s="71"/>
       <c r="H33" s="71"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="71"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="69" t="s">
         <v>211</v>
       </c>
@@ -2492,8 +2499,9 @@
       </c>
       <c r="G34" s="71"/>
       <c r="H34" s="71"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="71"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="69" t="s">
         <v>214</v>
       </c>
@@ -2509,8 +2517,9 @@
       </c>
       <c r="G35" s="71"/>
       <c r="H35" s="71"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="71"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="69" t="s">
         <v>217</v>
       </c>
@@ -2526,6 +2535,7 @@
       </c>
       <c r="G36" s="71"/>
       <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="69" t="s">
@@ -2538,7 +2548,7 @@
       <c r="E38" s="55"/>
       <c r="F38" s="55"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="72" t="s">
         <v>221</v>
       </c>
@@ -2548,29 +2558,30 @@
       <c r="F40" s="72"/>
       <c r="G40" s="72"/>
       <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_Startup.xlsx
@@ -20,19 +20,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="235">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -393,6 +393,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -462,6 +483,21 @@
     <t>Cumulative Profit</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
+  </si>
+  <si>
     <t>Break-even</t>
   </si>
   <si>
@@ -522,7 +558,10 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from assumptions</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -721,7 +760,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -819,6 +858,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -840,6 +885,13 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -967,7 +1019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1009,6 +1061,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1016,20 +1074,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1049,7 +1108,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1081,7 +1140,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1870,7 +1929,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1881,691 +1940,702 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="52" t="s">
+      <c r="B3" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D7" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E7" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F7" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G7" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="52" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="53">
-        <v>12</v>
-      </c>
-      <c r="D7" s="53">
-        <v>18</v>
-      </c>
-      <c r="E7" s="53">
-        <v>22</v>
-      </c>
-      <c r="F7" s="53">
-        <v>25</v>
-      </c>
-      <c r="G7" s="53">
-        <v>25</v>
+      <c r="H7" s="55" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="54">
-        <v>221600</v>
-      </c>
-      <c r="D8" s="54">
-        <v>340512</v>
-      </c>
-      <c r="E8" s="54">
-        <v>427946</v>
-      </c>
-      <c r="F8" s="54">
-        <v>500518</v>
-      </c>
-      <c r="G8" s="54">
-        <v>516085</v>
+        <v>179</v>
+      </c>
+      <c r="C8" s="56">
+        <v>12</v>
+      </c>
+      <c r="D8" s="56">
+        <v>18</v>
+      </c>
+      <c r="E8" s="56">
+        <v>22</v>
+      </c>
+      <c r="F8" s="56">
+        <v>25</v>
+      </c>
+      <c r="G8" s="56">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="54">
-        <v>118934</v>
-      </c>
-      <c r="D9" s="54">
-        <v>147003</v>
-      </c>
-      <c r="E9" s="54">
-        <v>151413</v>
-      </c>
-      <c r="F9" s="54">
-        <v>155955</v>
-      </c>
-      <c r="G9" s="54">
-        <v>160634</v>
+        <v>180</v>
+      </c>
+      <c r="C9" s="57">
+        <v>221600</v>
+      </c>
+      <c r="D9" s="57">
+        <v>340512</v>
+      </c>
+      <c r="E9" s="57">
+        <v>427946</v>
+      </c>
+      <c r="F9" s="57">
+        <v>500518</v>
+      </c>
+      <c r="G9" s="57">
+        <v>516085</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="54">
-        <v>48600</v>
-      </c>
-      <c r="D10" s="54">
-        <v>54963</v>
-      </c>
-      <c r="E10" s="54">
-        <v>59946</v>
-      </c>
-      <c r="F10" s="54">
-        <v>64338</v>
-      </c>
-      <c r="G10" s="54">
-        <v>66214</v>
+        <v>181</v>
+      </c>
+      <c r="C10" s="57">
+        <v>118934</v>
+      </c>
+      <c r="D10" s="57">
+        <v>147003</v>
+      </c>
+      <c r="E10" s="57">
+        <v>151413</v>
+      </c>
+      <c r="F10" s="57">
+        <v>155955</v>
+      </c>
+      <c r="G10" s="57">
+        <v>160634</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="54">
+        <v>17</v>
+      </c>
+      <c r="C11" s="57">
+        <v>48600</v>
+      </c>
+      <c r="D11" s="57">
+        <v>54963</v>
+      </c>
+      <c r="E11" s="57">
+        <v>59946</v>
+      </c>
+      <c r="F11" s="57">
+        <v>64338</v>
+      </c>
+      <c r="G11" s="57">
+        <v>66214</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="57">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D12" s="57">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="54">
+      <c r="E12" s="57">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F12" s="57">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G12" s="57">
         <v>6959.808550594178</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="56">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="59">
         <v>47106</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D13" s="59">
         <v>131586</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E13" s="59">
         <v>209627</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F13" s="59">
         <v>273265</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G13" s="59">
         <v>282277</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="56">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="59">
         <v>47106</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D14" s="59">
         <v>178692</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E14" s="59">
         <v>388319</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F14" s="59">
         <v>661584</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G14" s="59">
         <v>943861</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="57">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="60">
         <v>0.21257220216606498</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D15" s="60">
         <v>0.38643572032703694</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E15" s="60">
         <v>0.4898445130927734</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F15" s="60">
         <v>0.5459643809013862</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G15" s="60">
         <v>0.5469583498842245</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="58">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="61">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D16" s="61">
         <v>18917.333333333332</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E16" s="61">
         <v>19452.090909090908</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F16" s="61">
         <v>20020.72</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G16" s="61">
         <v>20643.4</v>
       </c>
-      <c r="H15" s="59" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="60">
+      <c r="H16" s="62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="63">
         <v>14541.150712549514</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D17" s="63">
         <v>11606.989363921899</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E17" s="63">
         <v>9923.582206845189</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F17" s="63">
         <v>9090.112342023767</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G17" s="63">
         <v>9352.312342023766</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="54">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="57">
         <v>500</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D18" s="57">
         <v>515</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E18" s="57">
         <v>530</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F18" s="57">
         <v>546</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G18" s="57">
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="61">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="64">
         <v>3000</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D19" s="64">
         <v>2058.6666666666665</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E19" s="61">
         <v>1733.6818181818182</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F19" s="61">
         <v>1570.1924</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G19" s="61">
         <v>1615.9705720000002</v>
       </c>
-      <c r="H18" s="59" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="62">
+      <c r="H19" s="62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="65">
         <v>3925.5</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D20" s="65">
         <v>7310.333333333333</v>
       </c>
-      <c r="E19" s="62">
+      <c r="E20" s="65">
         <v>9528.5</v>
       </c>
-      <c r="F19" s="62">
+      <c r="F20" s="65">
         <v>10930.6</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G20" s="65">
         <v>11291.08</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="57">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="60">
         <v>0.5367057761732852</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D21" s="60">
         <v>0.43171165773893433</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E21" s="60">
         <v>0.3538133315885649</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F21" s="60">
         <v>0.31158719566529075</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G21" s="60">
         <v>0.3112549289361249</v>
       </c>
-      <c r="H20" s="59" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="63">
+      <c r="H21" s="62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="66">
         <v>0.1624548736462094</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D22" s="60">
         <v>0.10882435861291231</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E22" s="60">
         <v>0.08912573081650489</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F22" s="60">
         <v>0.07842836821053388</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G22" s="60">
         <v>0.07828025286532257</v>
       </c>
-      <c r="H21" s="59" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="57">
+      <c r="H22" s="62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="60">
         <v>0.24398014440433213</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D23" s="60">
         <v>0.4068755286157316</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E23" s="60">
         <v>0.5061082473022297</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F23" s="60">
         <v>0.5598699747062044</v>
       </c>
-      <c r="G22" s="57">
+      <c r="G23" s="60">
         <v>0.5604445004214422</v>
       </c>
-      <c r="H22" s="59" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="64">
+      <c r="H23" s="62" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="67">
         <v>3</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D24" s="67">
         <v>3</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E24" s="67">
         <v>3</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F24" s="67">
         <v>3</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G24" s="67">
         <v>3</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" s="65">
+      <c r="H24" s="62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="68">
         <v>7.768317132140687</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D25" s="68">
         <v>19.906582055072757</v>
       </c>
-      <c r="E24" s="65">
+      <c r="E25" s="68">
         <v>31.11967785112557</v>
       </c>
-      <c r="F24" s="65">
+      <c r="F25" s="68">
         <v>40.26332017079355</v>
       </c>
-      <c r="G24" s="65">
+      <c r="G25" s="68">
         <v>41.558183374930195</v>
       </c>
-      <c r="H24" s="59" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" s="40" t="str">
+      <c r="H25" s="62" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="42" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="66" t="str">
+      <c r="D26" s="69" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="66" t="str">
+      <c r="E26" s="69" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="66" t="str">
+      <c r="F26" s="69" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="66" t="str">
+      <c r="G26" s="69" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H26" s="62" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
-        <v>190</v>
-      </c>
-      <c r="C26" s="67">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="70">
         <v>3</v>
       </c>
-      <c r="D26" s="67">
+      <c r="D27" s="70">
         <v>10</v>
       </c>
-      <c r="E26" s="68">
+      <c r="E27" s="71">
         <v>21</v>
       </c>
-      <c r="F26" s="64">
+      <c r="F27" s="67">
         <v>35</v>
       </c>
-      <c r="G26" s="64">
+      <c r="G27" s="67">
         <v>48</v>
       </c>
-      <c r="H26" s="59" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="64">
+      <c r="H27" s="62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="67">
         <v>99</v>
       </c>
-      <c r="D27" s="64">
+      <c r="D28" s="67">
         <v>312</v>
       </c>
-      <c r="E27" s="64">
+      <c r="E28" s="67">
         <v>649</v>
       </c>
-      <c r="F27" s="64">
+      <c r="F28" s="67">
         <v>1063</v>
       </c>
-      <c r="G27" s="64">
+      <c r="G28" s="67">
         <v>1473</v>
       </c>
-      <c r="H27" s="59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
+      <c r="H28" s="62" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
+      <c r="B31" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="69" t="s">
-        <v>205</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D32" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="E32" s="70"/>
-      <c r="F32" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
+      <c r="B32" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D32" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="73"/>
+      <c r="F32" s="74" t="s">
+        <v>217</v>
+      </c>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D33" s="70" t="s">
-        <v>209</v>
-      </c>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71" t="s">
-        <v>210</v>
-      </c>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
+      <c r="B33" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" s="73" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="73"/>
+      <c r="F33" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="69" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D34" s="70" t="s">
+      <c r="B34" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="E34" s="70"/>
-      <c r="F34" s="71" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
+      <c r="D34" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D35" s="70" t="s">
-        <v>215</v>
-      </c>
-      <c r="E35" s="70"/>
-      <c r="F35" s="71" t="s">
-        <v>216</v>
-      </c>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
+      <c r="B35" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="73"/>
+      <c r="F35" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="D36" s="70" t="s">
-        <v>218</v>
-      </c>
-      <c r="E36" s="70"/>
-      <c r="F36" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="69" t="s">
+      <c r="B36" s="72" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="73"/>
+      <c r="F36" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D37" s="73" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" s="73"/>
+      <c r="F37" s="74" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="72" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
+      <c r="C39" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2580,95 +2650,97 @@
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C25:G25">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C25&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1.15</formula>
+      <formula>C25&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1.15</formula>
+      <formula>C25&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3037,11 +3109,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3349,9 +3421,154 @@
         <v>160634</v>
       </c>
     </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="30">
+        <v>55000</v>
+      </c>
+      <c r="C25" s="30">
+        <v>56650</v>
+      </c>
+      <c r="D25" s="30">
+        <v>58350</v>
+      </c>
+      <c r="E25" s="30">
+        <v>60100</v>
+      </c>
+      <c r="F25" s="30">
+        <v>61903</v>
+      </c>
+      <c r="G25" s="30">
+        <f>SUM(B25:F25)</f>
+        <v>292003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="30">
+        <v>70208</v>
+      </c>
+      <c r="C26" s="30">
+        <v>72314</v>
+      </c>
+      <c r="D26" s="30">
+        <v>74484</v>
+      </c>
+      <c r="E26" s="30">
+        <v>76718</v>
+      </c>
+      <c r="F26" s="30">
+        <v>79019</v>
+      </c>
+      <c r="G26" s="30">
+        <f>SUM(B26:F26)</f>
+        <v>372743</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="30">
+        <v>70000</v>
+      </c>
+      <c r="C27" s="30">
+        <v>72000</v>
+      </c>
+      <c r="D27" s="30">
+        <v>74000</v>
+      </c>
+      <c r="E27" s="30">
+        <v>76000</v>
+      </c>
+      <c r="F27" s="30">
+        <v>79000</v>
+      </c>
+      <c r="G27" s="30">
+        <f>SUM(B27:F27)</f>
+        <v>371000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="30">
+        <v>89355</v>
+      </c>
+      <c r="C28" s="30">
+        <v>91908</v>
+      </c>
+      <c r="D28" s="30">
+        <v>94461</v>
+      </c>
+      <c r="E28" s="30">
+        <v>97014</v>
+      </c>
+      <c r="F28" s="30">
+        <v>100844</v>
+      </c>
+      <c r="G28" s="30">
+        <f>SUM(B28:F28)</f>
+        <v>473582</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="10">
+        <v>19148</v>
+      </c>
+      <c r="C29" s="10">
+        <v>19594</v>
+      </c>
+      <c r="D29" s="10">
+        <v>19977</v>
+      </c>
+      <c r="E29" s="10">
+        <v>20296</v>
+      </c>
+      <c r="F29" s="10">
+        <v>21824</v>
+      </c>
+      <c r="G29" s="10">
+        <f>SUM(B29:F29)</f>
+        <v>100839</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3421,7 +3638,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3431,7 +3648,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B4" s="30">
         <f>500*Assumptions!B23</f>
@@ -3456,7 +3673,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3481,7 +3698,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3491,7 +3708,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B7" s="30">
         <f>300*Assumptions!B23</f>
@@ -3516,7 +3733,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3541,7 +3758,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3551,7 +3768,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B10" s="30">
         <f>2500*12</f>
@@ -3576,7 +3793,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B11" s="30">
         <f>300*12</f>
@@ -3601,7 +3818,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B12" s="30">
         <v>2400</v>
@@ -3621,7 +3838,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -3646,7 +3863,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3656,7 +3873,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B15" s="30">
         <v>3000</v>
@@ -3676,7 +3893,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
@@ -3701,7 +3918,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B18" s="31">
         <f>B5+B8+B13+B16</f>
@@ -3768,7 +3985,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3778,7 +3995,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B3" s="30">
         <v>6959.808550594178</v>
@@ -3798,7 +4015,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B4" s="31">
         <f>SUM(B3:B3)</f>
@@ -3836,11 +4053,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3865,7 +4082,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B17</f>
@@ -3890,7 +4107,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B22</f>
@@ -3965,7 +4182,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -3990,7 +4207,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4015,7 +4232,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4042,48 +4259,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="41">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="41" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="30">
+        <v>70208</v>
+      </c>
+      <c r="C12" s="30">
+        <v>72314</v>
+      </c>
+      <c r="D12" s="30">
+        <v>74484</v>
+      </c>
+      <c r="E12" s="30">
+        <v>76718</v>
+      </c>
+      <c r="F12" s="30">
+        <v>79019</v>
+      </c>
+      <c r="G12" s="30">
+        <f>SUM(B12:F12)</f>
+        <v>372743</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="30">
+        <v>89355</v>
+      </c>
+      <c r="C13" s="30">
+        <v>91908</v>
+      </c>
+      <c r="D13" s="30">
+        <v>94461</v>
+      </c>
+      <c r="E13" s="30">
+        <v>97014</v>
+      </c>
+      <c r="F13" s="30">
+        <v>100844</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(B13:F13)</f>
+        <v>473582</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="10">
+        <v>19148</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19594</v>
+      </c>
+      <c r="D14" s="10">
+        <v>19977</v>
+      </c>
+      <c r="E14" s="10">
+        <v>20296</v>
+      </c>
+      <c r="F14" s="10">
+        <v>21824</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>100839</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F16" s="43" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4106,18 +4422,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>143</v>
+      <c r="A2" s="45" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,12 +4515,12 @@
         <v>41</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4259,24 +4575,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="44">
+        <v>159</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.5</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="46">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="46">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F18" s="44" t="str">
+      <c r="F18" s="46" t="str">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0</v>
       </c>
@@ -4303,7 +4619,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4328,7 +4644,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4378,7 +4694,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4403,32 +4719,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="45">
+        <v>145</v>
+      </c>
+      <c r="B25" s="47">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="45">
+      <c r="C25" s="47">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="47">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="47">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="47">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4478,7 +4794,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4488,7 +4804,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4513,57 +4829,57 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="44">
+        <v>162</v>
+      </c>
+      <c r="B31" s="46">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="46">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" s="44">
+        <v>163</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="46">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="46">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="46">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="46">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B33" s="12">
         <f>IF(B21=0,0,B25/B21)</f>
@@ -4588,7 +4904,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4598,61 +4914,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B36" s="44">
+        <v>166</v>
+      </c>
+      <c r="B36" s="46">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="46">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="46">
         <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B37" s="44">
+        <v>167</v>
+      </c>
+      <c r="B37" s="46">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="46">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="46">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="46">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="46">
         <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="44">
+        <v>168</v>
+      </c>
+      <c r="B38" s="46">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="46">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="46">
         <v>0.017438987763643585</v>
       </c>
     </row>
@@ -4700,26 +5016,26 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="B4" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="3">
